--- a/analysis/data/raw_data/Scar_orientation_data.xlsx
+++ b/analysis/data/raw_data/Scar_orientation_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\SPHARM_analysis\analysis\data\raw_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C18DB131-80A5-48FA-A7F6-AD749B144E70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4481BD75-1FDD-46FF-867B-165A64CCFFB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9806E38F-78FD-4181-A145-E11E6146B3D0}"/>
   </bookViews>
@@ -701,7 +701,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13CC4D35-A102-4762-A24C-8854C87E9CAE}">
-  <dimension ref="A1:S273"/>
+  <dimension ref="A1:T273"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="21.75" style="2" customWidth="1"/>
@@ -714,7 +714,7 @@
     <col min="20" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -773,7 +773,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>43</v>
       </c>
@@ -831,8 +831,9 @@
       <c r="S2" s="2" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T2" s="6"/>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>43</v>
       </c>
@@ -891,7 +892,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>43</v>
       </c>
@@ -950,7 +951,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>43</v>
       </c>
@@ -1009,7 +1010,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>43</v>
       </c>
@@ -1068,7 +1069,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>43</v>
       </c>
@@ -1127,7 +1128,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>43</v>
       </c>
@@ -1186,7 +1187,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>43</v>
       </c>
@@ -1245,7 +1246,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>43</v>
       </c>
@@ -1304,7 +1305,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>43</v>
       </c>
@@ -1363,7 +1364,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>43</v>
       </c>
@@ -1422,7 +1423,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>43</v>
       </c>
@@ -1481,7 +1482,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>43</v>
       </c>
@@ -1540,7 +1541,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>43</v>
       </c>
@@ -1599,7 +1600,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>43</v>
       </c>

--- a/analysis/data/raw_data/Scar_orientation_data.xlsx
+++ b/analysis/data/raw_data/Scar_orientation_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\SPHARM_analysis\analysis\data\raw_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4481BD75-1FDD-46FF-867B-165A64CCFFB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10333623-034F-4A77-89A0-349CF9602EE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9806E38F-78FD-4181-A145-E11E6146B3D0}"/>
   </bookViews>
@@ -242,10 +242,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>IM_Multifacial</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>multifacial</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -278,6 +274,10 @@
   </si>
   <si>
     <t>cylindrical_bipolar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IM_Multiplatform </t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -3136,7 +3136,7 @@
     </row>
     <row r="42" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B42" s="6">
         <v>0.4587</v>
@@ -3195,7 +3195,7 @@
     </row>
     <row r="43" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B43" s="6">
         <v>0.4587</v>
@@ -3254,7 +3254,7 @@
     </row>
     <row r="44" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B44" s="6">
         <v>0.4587</v>
@@ -3313,7 +3313,7 @@
     </row>
     <row r="45" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B45" s="6">
         <v>0.4587</v>
@@ -3372,7 +3372,7 @@
     </row>
     <row r="46" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B46" s="6">
         <v>0.4587</v>
@@ -3431,7 +3431,7 @@
     </row>
     <row r="47" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B47" s="6">
         <v>0.4587</v>
@@ -3490,7 +3490,7 @@
     </row>
     <row r="48" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B48" s="6">
         <v>0.4587</v>
@@ -3549,7 +3549,7 @@
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B49" s="6">
         <v>0.4587</v>
@@ -3608,7 +3608,7 @@
     </row>
     <row r="50" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B50" s="6">
         <v>0.4587</v>
@@ -3667,7 +3667,7 @@
     </row>
     <row r="51" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A51" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B51" s="6">
         <v>0.4587</v>
@@ -3726,7 +3726,7 @@
     </row>
     <row r="52" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B52" s="6">
         <v>0.4587</v>
@@ -3785,7 +3785,7 @@
     </row>
     <row r="53" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B53" s="6">
         <v>0.4587</v>
@@ -3844,7 +3844,7 @@
     </row>
     <row r="54" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B54" s="6">
         <v>0.4587</v>
@@ -3898,12 +3898,12 @@
         <v>0.96619999999999995</v>
       </c>
       <c r="S54" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="55" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A55" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B55" s="6">
         <v>0.4587</v>
@@ -3957,12 +3957,12 @@
         <v>0.96699999999999997</v>
       </c>
       <c r="S55" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="56" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A56" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B56" s="6">
         <v>0.4587</v>
@@ -4016,12 +4016,12 @@
         <v>0.96619999999999995</v>
       </c>
       <c r="S56" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="57" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A57" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B57" s="6">
         <v>0.4587</v>
@@ -4075,12 +4075,12 @@
         <v>0.96609999999999996</v>
       </c>
       <c r="S57" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="58" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B58" s="6">
         <v>0.4587</v>
@@ -4134,12 +4134,12 @@
         <v>0.96609999999999996</v>
       </c>
       <c r="S58" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="59" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B59" s="6">
         <v>0.4587</v>
@@ -4193,12 +4193,12 @@
         <v>0.96609999999999996</v>
       </c>
       <c r="S59" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="60" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B60" s="6">
         <v>0.4587</v>
@@ -4252,12 +4252,12 @@
         <v>0.96609999999999996</v>
       </c>
       <c r="S60" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="61" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B61" s="6">
         <v>0.4587</v>
@@ -4311,12 +4311,12 @@
         <v>0.96619999999999995</v>
       </c>
       <c r="S61" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="62" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B62" s="6">
         <v>0.4587</v>
@@ -4370,12 +4370,12 @@
         <v>0.96619999999999995</v>
       </c>
       <c r="S62" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="63" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A63" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B63" s="6">
         <v>0.4587</v>
@@ -4429,12 +4429,12 @@
         <v>0.96619999999999995</v>
       </c>
       <c r="S63" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="64" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A64" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B64" s="6">
         <v>0.4587</v>
@@ -4488,12 +4488,12 @@
         <v>0.96619999999999995</v>
       </c>
       <c r="S64" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="65" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A65" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B65" s="6">
         <v>0.4587</v>
@@ -4547,12 +4547,12 @@
         <v>0.96630000000000005</v>
       </c>
       <c r="S65" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="66" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A66" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B66" s="6">
         <v>0.4587</v>
@@ -4606,12 +4606,12 @@
         <v>0</v>
       </c>
       <c r="S66" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="67" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A67" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B67" s="6">
         <v>-2.2359</v>
@@ -4670,7 +4670,7 @@
     </row>
     <row r="68" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A68" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B68" s="6">
         <v>-2.2359</v>
@@ -4729,7 +4729,7 @@
     </row>
     <row r="69" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A69" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B69" s="6">
         <v>-2.2359</v>
@@ -4788,7 +4788,7 @@
     </row>
     <row r="70" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A70" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B70" s="6">
         <v>-2.2359</v>
@@ -4847,7 +4847,7 @@
     </row>
     <row r="71" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A71" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B71" s="6">
         <v>-2.2359</v>
@@ -4906,7 +4906,7 @@
     </row>
     <row r="72" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A72" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B72" s="6">
         <v>-2.2359</v>
@@ -4965,7 +4965,7 @@
     </row>
     <row r="73" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A73" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B73" s="6">
         <v>-2.2359</v>
@@ -5024,7 +5024,7 @@
     </row>
     <row r="74" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A74" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B74" s="6">
         <v>-2.2359</v>
@@ -5083,7 +5083,7 @@
     </row>
     <row r="75" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A75" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B75" s="6">
         <v>-2.2359</v>
@@ -5142,7 +5142,7 @@
     </row>
     <row r="76" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A76" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B76" s="6">
         <v>-2.2359</v>
@@ -5201,7 +5201,7 @@
     </row>
     <row r="77" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A77" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B77" s="6">
         <v>-2.2359</v>
@@ -5260,7 +5260,7 @@
     </row>
     <row r="78" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A78" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B78" s="6">
         <v>-2.2359</v>
@@ -5319,7 +5319,7 @@
     </row>
     <row r="79" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A79" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B79" s="6">
         <v>-2.2359</v>
@@ -5373,12 +5373,12 @@
         <v>-1</v>
       </c>
       <c r="S79" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="80" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A80" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B80" s="6">
         <v>-2.2359</v>
@@ -5432,12 +5432,12 @@
         <v>-1</v>
       </c>
       <c r="S80" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="81" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A81" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B81" s="6">
         <v>-2.2359</v>
@@ -5491,12 +5491,12 @@
         <v>-1</v>
       </c>
       <c r="S81" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="82" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A82" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B82" s="6">
         <v>-2.2359</v>
@@ -5550,12 +5550,12 @@
         <v>-1</v>
       </c>
       <c r="S82" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="83" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A83" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B83" s="6">
         <v>-2.2359</v>
@@ -5609,12 +5609,12 @@
         <v>-1</v>
       </c>
       <c r="S83" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="84" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A84" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B84" s="6">
         <v>-2.2359</v>
@@ -5668,12 +5668,12 @@
         <v>-1</v>
       </c>
       <c r="S84" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="85" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A85" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B85" s="6">
         <v>-2.2359</v>
@@ -5727,12 +5727,12 @@
         <v>-1</v>
       </c>
       <c r="S85" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="86" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A86" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B86" s="6">
         <v>-2.2359</v>
@@ -5786,12 +5786,12 @@
         <v>-1</v>
       </c>
       <c r="S86" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="87" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A87" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B87" s="6">
         <v>-2.2359</v>
@@ -5845,12 +5845,12 @@
         <v>-1</v>
       </c>
       <c r="S87" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="88" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A88" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B88" s="6">
         <v>-2.2359</v>
@@ -5904,12 +5904,12 @@
         <v>-1</v>
       </c>
       <c r="S88" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="89" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A89" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B89" s="6">
         <v>-2.2359</v>
@@ -5963,12 +5963,12 @@
         <v>-1</v>
       </c>
       <c r="S89" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="90" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A90" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B90" s="6">
         <v>-2.2359</v>
@@ -6022,12 +6022,12 @@
         <v>-1</v>
       </c>
       <c r="S90" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="91" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A91" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B91" s="6">
         <v>-2.2359</v>
@@ -6081,12 +6081,12 @@
         <v>0</v>
       </c>
       <c r="S91" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="92" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A92" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B92" s="6">
         <v>-2.2359</v>
@@ -6140,12 +6140,12 @@
         <v>-1</v>
       </c>
       <c r="S92" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="93" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A93" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B93" s="6">
         <v>-2.2359</v>
@@ -6199,12 +6199,12 @@
         <v>1</v>
       </c>
       <c r="S93" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="94" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A94" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B94" s="6">
         <v>-2.2359</v>
@@ -6258,12 +6258,12 @@
         <v>-1</v>
       </c>
       <c r="S94" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="95" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A95" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B95" s="6">
         <v>-2.2359</v>
@@ -6317,12 +6317,12 @@
         <v>1</v>
       </c>
       <c r="S95" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="96" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A96" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B96" s="6">
         <v>-2.2359</v>
@@ -6376,12 +6376,12 @@
         <v>-1</v>
       </c>
       <c r="S96" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="97" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A97" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B97" s="6">
         <v>-2.2359</v>
@@ -6435,12 +6435,12 @@
         <v>1</v>
       </c>
       <c r="S97" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="98" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A98" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B98" s="6">
         <v>-2.2359</v>
@@ -6494,12 +6494,12 @@
         <v>-1</v>
       </c>
       <c r="S98" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="99" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A99" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B99" s="6">
         <v>-2.2359</v>
@@ -6553,12 +6553,12 @@
         <v>1</v>
       </c>
       <c r="S99" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="100" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A100" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B100" s="6">
         <v>-2.2359</v>
@@ -6612,12 +6612,12 @@
         <v>-1</v>
       </c>
       <c r="S100" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="101" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A101" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B101" s="6">
         <v>-2.2359</v>
@@ -6671,12 +6671,12 @@
         <v>1</v>
       </c>
       <c r="S101" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="102" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A102" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B102" s="6">
         <v>-2.2359</v>
@@ -6730,12 +6730,12 @@
         <v>-1</v>
       </c>
       <c r="S102" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="103" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A103" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B103" s="6">
         <v>-2.2359</v>
@@ -6789,7 +6789,7 @@
         <v>1</v>
       </c>
       <c r="S103" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="104" spans="1:19" x14ac:dyDescent="0.2">
@@ -11101,7 +11101,7 @@
     </row>
     <row r="177" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A177" s="2" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="B177" s="6">
         <v>15</v>
@@ -11155,12 +11155,12 @@
         <v>-0.99990000000000001</v>
       </c>
       <c r="S177" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="178" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A178" s="2" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="B178" s="6">
         <v>15</v>
@@ -11214,12 +11214,12 @@
         <v>0.99990000000000001</v>
       </c>
       <c r="S178" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="179" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A179" s="2" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="B179" s="6">
         <v>15</v>
@@ -11273,12 +11273,12 @@
         <v>-3.0200000000000001E-2</v>
       </c>
       <c r="S179" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="180" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A180" s="2" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="B180" s="6">
         <v>15</v>
@@ -11332,12 +11332,12 @@
         <v>1.4E-3</v>
       </c>
       <c r="S180" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="181" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A181" s="2" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="B181" s="6">
         <v>15</v>
@@ -11391,12 +11391,12 @@
         <v>-3.8E-3</v>
       </c>
       <c r="S181" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="182" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A182" s="2" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="B182" s="6">
         <v>15</v>
@@ -11450,7 +11450,7 @@
         <v>0</v>
       </c>
       <c r="S182" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="183" spans="1:19" x14ac:dyDescent="0.2">

--- a/analysis/data/raw_data/Scar_orientation_data.xlsx
+++ b/analysis/data/raw_data/Scar_orientation_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\SPHARM_analysis\analysis\data\raw_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79D90F50-8BA1-46C1-8052-7031EDFC2828}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A8D065A-158D-470B-9D04-B2B1F7F035BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{9806E38F-78FD-4181-A145-E11E6146B3D0}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1056" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1578" uniqueCount="120">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -248,6 +248,177 @@
   <si>
     <t>S27</t>
   </si>
+  <si>
+    <t>SDG_L2_489</t>
+  </si>
+  <si>
+    <t>SDG_L2_494</t>
+  </si>
+  <si>
+    <t>SDG_L3_1066</t>
+  </si>
+  <si>
+    <t>SDG_L3_1163</t>
+  </si>
+  <si>
+    <t>SDG_L3_1191</t>
+  </si>
+  <si>
+    <t>SDG_L3_1318</t>
+  </si>
+  <si>
+    <t>SDG_L3_1416</t>
+  </si>
+  <si>
+    <t>SDG_L3_1437</t>
+  </si>
+  <si>
+    <t>SDG_L3_1492</t>
+  </si>
+  <si>
+    <t>SDG_L3_1547</t>
+  </si>
+  <si>
+    <t>SDG_L3_155</t>
+  </si>
+  <si>
+    <t>SDG_L3_1677</t>
+  </si>
+  <si>
+    <t>SDG_L3_155</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SDG_L3_1748</t>
+  </si>
+  <si>
+    <t>SDG_L3_188</t>
+  </si>
+  <si>
+    <t>SDG_L4_1884</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SDG_L3_303</t>
+  </si>
+  <si>
+    <t>SDG_L3_434</t>
+  </si>
+  <si>
+    <t>SDG_L3_55</t>
+  </si>
+  <si>
+    <t>SDG_L3_636</t>
+  </si>
+  <si>
+    <t>SDG_L3_645</t>
+  </si>
+  <si>
+    <t>SDG_L3_804</t>
+  </si>
+  <si>
+    <t>SDG_L3_890</t>
+  </si>
+  <si>
+    <t>SDG_L3_978</t>
+  </si>
+  <si>
+    <t>SDG_L4_1916</t>
+  </si>
+  <si>
+    <t>SDG_L4_1951</t>
+  </si>
+  <si>
+    <t>SDG_L4_2001</t>
+  </si>
+  <si>
+    <t>SDG_L4_2004</t>
+  </si>
+  <si>
+    <t>SDG_L4_2158</t>
+  </si>
+  <si>
+    <t>SDG_L4_2164</t>
+  </si>
+  <si>
+    <t>SDG_L4_2182</t>
+  </si>
+  <si>
+    <t>SDG_L4_2213</t>
+  </si>
+  <si>
+    <t>SDG_L4_2292</t>
+  </si>
+  <si>
+    <t>SDG_L4_2389</t>
+  </si>
+  <si>
+    <t>SDG_L4_2527</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SDG_L4_2733</t>
+  </si>
+  <si>
+    <t>SDG_L4_2818</t>
+  </si>
+  <si>
+    <t>SDG_L4_3095</t>
+  </si>
+  <si>
+    <t>SDG_L4_3155</t>
+  </si>
+  <si>
+    <t>SDG_L4_3192</t>
+  </si>
+  <si>
+    <t>SDG_L4_3341</t>
+  </si>
+  <si>
+    <t>SDG_L4_3342</t>
+  </si>
+  <si>
+    <t>SDG_L4_3506</t>
+  </si>
+  <si>
+    <t>SDG_L4_3513</t>
+  </si>
+  <si>
+    <t>SDG_L4_3821</t>
+  </si>
+  <si>
+    <t>SDG_L4_3952</t>
+  </si>
+  <si>
+    <t>SDG_L4_3971</t>
+  </si>
+  <si>
+    <t>SDG_L4_4262</t>
+  </si>
+  <si>
+    <t>SDG_L4_4386</t>
+  </si>
+  <si>
+    <t>SDG_L4_4460</t>
+  </si>
+  <si>
+    <t>SDG_L4_4604</t>
+  </si>
+  <si>
+    <t>SDG_L4_4858</t>
+  </si>
+  <si>
+    <t>SDG_L4_4583</t>
+  </si>
+  <si>
+    <t>SDG_L4_1788</t>
+  </si>
+  <si>
+    <t>SDG_L4_2165</t>
+  </si>
+  <si>
+    <t>SDG_L4_3283</t>
+  </si>
 </sst>
 </file>
 
@@ -331,7 +502,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -347,11 +518,75 @@
     <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="6">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -659,6 +894,53 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="350" row="4">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{018F7C0D-E229-40B2-96D7-498A8B135164}">
+  <we:reference id="wa200005502" version="1.0.0.12" store="zh-CN" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="wa200005502" version="1.0.0.12" store="wa200005502" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties>
+    <we:property name="docId" value="&quot;1aOfNZviyYXXiz7HosCYu&quot;"/>
+  </we:properties>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+  <we:extLst>
+    <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" uri="{7C84B067-C214-45C3-A712-C9D94CD141B2}">
+      <we:customFunctionIdList>
+        <we:customFunctionIds>_xldudf_GPT</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_CREATE_PROMPT</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_LIST</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_HLIST</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_CLASSIFY</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_TRANSLATE</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_EXTRACT</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_TAG</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_CONVERT</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_FORMAT</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_SUMMARIZE</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_TABLE</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_FILL</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_SPLIT</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_HSPLIT</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_EDIT</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_MATCH</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_VISION</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_WEB</we:customFunctionIds>
+      </we:customFunctionIdList>
+    </a:ext>
+  </we:extLst>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{361C2C89-3419-4E0B-82ED-85AD1B887A83}">
   <dimension ref="A1:O182"/>
@@ -9226,10 +9508,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13CC4D35-A102-4762-A24C-8854C87E9CAE}">
-  <dimension ref="A1:N485"/>
+  <dimension ref="A1:N504"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="7.375" style="3" customWidth="1"/>
+    <col min="1" max="1" width="14" style="3" customWidth="1"/>
     <col min="2" max="7" width="9" style="4"/>
     <col min="8" max="8" width="7" style="3" customWidth="1"/>
     <col min="9" max="14" width="9" style="4"/>
@@ -9281,8 +9563,8 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A2" s="3">
-        <v>55</v>
+      <c r="A2" s="3" t="s">
+        <v>82</v>
       </c>
       <c r="B2" s="4">
         <v>-25.6599</v>
@@ -9325,8 +9607,8 @@
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A3" s="3">
-        <v>55</v>
+      <c r="A3" s="3" t="s">
+        <v>82</v>
       </c>
       <c r="B3" s="4">
         <v>-25.6599</v>
@@ -9369,8 +9651,8 @@
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A4" s="3">
-        <v>55</v>
+      <c r="A4" s="3" t="s">
+        <v>82</v>
       </c>
       <c r="B4" s="4">
         <v>-25.6599</v>
@@ -9413,8 +9695,8 @@
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A5" s="3">
-        <v>55</v>
+      <c r="A5" s="3" t="s">
+        <v>82</v>
       </c>
       <c r="B5" s="4">
         <v>-25.6599</v>
@@ -9457,8 +9739,8 @@
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A6" s="3">
-        <v>55</v>
+      <c r="A6" s="3" t="s">
+        <v>82</v>
       </c>
       <c r="B6" s="4">
         <v>-25.6599</v>
@@ -9501,8 +9783,8 @@
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A7" s="3">
-        <v>55</v>
+      <c r="A7" s="3" t="s">
+        <v>82</v>
       </c>
       <c r="B7" s="4">
         <v>-25.6599</v>
@@ -9545,8 +9827,8 @@
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A8" s="3">
-        <v>155</v>
+      <c r="A8" s="3" t="s">
+        <v>74</v>
       </c>
       <c r="B8" s="4">
         <v>-16.466000000000001</v>
@@ -9589,8 +9871,8 @@
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A9" s="3">
-        <v>155</v>
+      <c r="A9" s="3" t="s">
+        <v>74</v>
       </c>
       <c r="B9" s="4">
         <v>-16.466000000000001</v>
@@ -9633,8 +9915,8 @@
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A10" s="3">
-        <v>155</v>
+      <c r="A10" s="3" t="s">
+        <v>74</v>
       </c>
       <c r="B10" s="4">
         <v>-16.466000000000001</v>
@@ -9677,8 +9959,8 @@
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A11" s="3">
-        <v>155</v>
+      <c r="A11" s="3" t="s">
+        <v>74</v>
       </c>
       <c r="B11" s="4">
         <v>-16.466000000000001</v>
@@ -9721,8 +10003,8 @@
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A12" s="3">
-        <v>155</v>
+      <c r="A12" s="3" t="s">
+        <v>74</v>
       </c>
       <c r="B12" s="4">
         <v>-16.466000000000001</v>
@@ -9765,8 +10047,8 @@
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A13" s="3">
-        <v>155</v>
+      <c r="A13" s="3" t="s">
+        <v>74</v>
       </c>
       <c r="B13" s="4">
         <v>-16.466000000000001</v>
@@ -9809,8 +10091,8 @@
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A14" s="3">
-        <v>188</v>
+      <c r="A14" s="3" t="s">
+        <v>78</v>
       </c>
       <c r="B14" s="4">
         <v>-32.7074</v>
@@ -9853,8 +10135,8 @@
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A15" s="3">
-        <v>188</v>
+      <c r="A15" s="3" t="s">
+        <v>78</v>
       </c>
       <c r="B15" s="4">
         <v>-32.7074</v>
@@ -9897,8 +10179,8 @@
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A16" s="3">
-        <v>188</v>
+      <c r="A16" s="3" t="s">
+        <v>78</v>
       </c>
       <c r="B16" s="4">
         <v>-32.7074</v>
@@ -9941,8 +10223,8 @@
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A17" s="3">
-        <v>188</v>
+      <c r="A17" s="3" t="s">
+        <v>78</v>
       </c>
       <c r="B17" s="4">
         <v>-32.7074</v>
@@ -9985,8 +10267,8 @@
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A18" s="3">
-        <v>188</v>
+      <c r="A18" s="3" t="s">
+        <v>78</v>
       </c>
       <c r="B18" s="4">
         <v>-32.7074</v>
@@ -10029,8 +10311,8 @@
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A19" s="3">
-        <v>188</v>
+      <c r="A19" s="3" t="s">
+        <v>78</v>
       </c>
       <c r="B19" s="4">
         <v>-32.7074</v>
@@ -10073,8 +10355,8 @@
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A20" s="3">
-        <v>188</v>
+      <c r="A20" s="3" t="s">
+        <v>78</v>
       </c>
       <c r="B20" s="4">
         <v>-32.7074</v>
@@ -10117,8 +10399,8 @@
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A21" s="3">
-        <v>434</v>
+      <c r="A21" s="3" t="s">
+        <v>81</v>
       </c>
       <c r="B21" s="4">
         <v>-5.5258000000000003</v>
@@ -10161,8 +10443,8 @@
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A22" s="3">
-        <v>434</v>
+      <c r="A22" s="3" t="s">
+        <v>81</v>
       </c>
       <c r="B22" s="4">
         <v>-5.5258000000000003</v>
@@ -10205,8 +10487,8 @@
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A23" s="3">
-        <v>434</v>
+      <c r="A23" s="3" t="s">
+        <v>81</v>
       </c>
       <c r="B23" s="4">
         <v>-5.5258000000000003</v>
@@ -10249,8 +10531,8 @@
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A24" s="3">
-        <v>434</v>
+      <c r="A24" s="3" t="s">
+        <v>81</v>
       </c>
       <c r="B24" s="4">
         <v>-5.5258000000000003</v>
@@ -10293,8 +10575,8 @@
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A25" s="3">
-        <v>434</v>
+      <c r="A25" s="3" t="s">
+        <v>81</v>
       </c>
       <c r="B25" s="4">
         <v>-5.5258000000000003</v>
@@ -10337,8 +10619,8 @@
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A26" s="3">
-        <v>434</v>
+      <c r="A26" s="3" t="s">
+        <v>81</v>
       </c>
       <c r="B26" s="4">
         <v>-5.5258000000000003</v>
@@ -10381,8 +10663,8 @@
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A27" s="3">
-        <v>804</v>
+      <c r="A27" s="3" t="s">
+        <v>85</v>
       </c>
       <c r="B27" s="4">
         <v>-17.612400000000001</v>
@@ -10425,8 +10707,8 @@
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A28" s="3">
-        <v>804</v>
+      <c r="A28" s="3" t="s">
+        <v>85</v>
       </c>
       <c r="B28" s="4">
         <v>-17.612400000000001</v>
@@ -10469,8 +10751,8 @@
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A29" s="3">
-        <v>804</v>
+      <c r="A29" s="3" t="s">
+        <v>85</v>
       </c>
       <c r="B29" s="4">
         <v>-17.612400000000001</v>
@@ -10513,8 +10795,8 @@
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A30" s="3">
-        <v>804</v>
+      <c r="A30" s="3" t="s">
+        <v>85</v>
       </c>
       <c r="B30" s="4">
         <v>-17.612400000000001</v>
@@ -10557,8 +10839,8 @@
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A31" s="3">
-        <v>804</v>
+      <c r="A31" s="3" t="s">
+        <v>85</v>
       </c>
       <c r="B31" s="4">
         <v>-17.612400000000001</v>
@@ -10601,8 +10883,8 @@
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A32" s="3">
-        <v>804</v>
+      <c r="A32" s="3" t="s">
+        <v>85</v>
       </c>
       <c r="B32" s="4">
         <v>-17.612400000000001</v>
@@ -10645,8 +10927,8 @@
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A33" s="3">
-        <v>890</v>
+      <c r="A33" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="B33" s="4">
         <v>-17.9312</v>
@@ -10689,8 +10971,8 @@
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A34" s="3">
-        <v>890</v>
+      <c r="A34" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="B34" s="4">
         <v>-17.9312</v>
@@ -10733,8 +11015,8 @@
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A35" s="3">
-        <v>890</v>
+      <c r="A35" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="B35" s="4">
         <v>-17.9312</v>
@@ -10777,8 +11059,8 @@
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A36" s="3">
-        <v>890</v>
+      <c r="A36" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="B36" s="4">
         <v>-17.9312</v>
@@ -10821,8 +11103,8 @@
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A37" s="3">
-        <v>978</v>
+      <c r="A37" s="5" t="s">
+        <v>87</v>
       </c>
       <c r="B37" s="4">
         <v>-15.3475</v>
@@ -10865,8 +11147,8 @@
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A38" s="3">
-        <v>978</v>
+      <c r="A38" s="5" t="s">
+        <v>87</v>
       </c>
       <c r="B38" s="4">
         <v>-15.3475</v>
@@ -10909,8 +11191,8 @@
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A39" s="3">
-        <v>978</v>
+      <c r="A39" s="5" t="s">
+        <v>87</v>
       </c>
       <c r="B39" s="4">
         <v>-15.3475</v>
@@ -10953,8 +11235,8 @@
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A40" s="3">
-        <v>978</v>
+      <c r="A40" s="5" t="s">
+        <v>87</v>
       </c>
       <c r="B40" s="4">
         <v>-15.3475</v>
@@ -10997,8 +11279,8 @@
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A41" s="3">
-        <v>978</v>
+      <c r="A41" s="5" t="s">
+        <v>87</v>
       </c>
       <c r="B41" s="4">
         <v>-15.3475</v>
@@ -11041,8 +11323,8 @@
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A42" s="3">
-        <v>978</v>
+      <c r="A42" s="5" t="s">
+        <v>87</v>
       </c>
       <c r="B42" s="4">
         <v>-15.3475</v>
@@ -11085,8 +11367,8 @@
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A43" s="3">
-        <v>978</v>
+      <c r="A43" s="5" t="s">
+        <v>87</v>
       </c>
       <c r="B43" s="4">
         <v>-15.3475</v>
@@ -11129,8 +11411,8 @@
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A44" s="3">
-        <v>1066</v>
+      <c r="A44" s="3" t="s">
+        <v>66</v>
       </c>
       <c r="B44" s="4">
         <v>-5.5284000000000004</v>
@@ -11173,8 +11455,8 @@
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A45" s="3">
-        <v>1066</v>
+      <c r="A45" s="3" t="s">
+        <v>66</v>
       </c>
       <c r="B45" s="4">
         <v>-5.5284000000000004</v>
@@ -11217,8 +11499,8 @@
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A46" s="3">
-        <v>1066</v>
+      <c r="A46" s="3" t="s">
+        <v>66</v>
       </c>
       <c r="B46" s="4">
         <v>-5.5284000000000004</v>
@@ -11261,8 +11543,8 @@
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A47" s="3">
-        <v>1066</v>
+      <c r="A47" s="3" t="s">
+        <v>66</v>
       </c>
       <c r="B47" s="4">
         <v>-5.5284000000000004</v>
@@ -11305,8 +11587,8 @@
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A48" s="3">
-        <v>1066</v>
+      <c r="A48" s="3" t="s">
+        <v>66</v>
       </c>
       <c r="B48" s="4">
         <v>-5.5284000000000004</v>
@@ -11349,8 +11631,8 @@
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A49" s="3">
-        <v>1066</v>
+      <c r="A49" s="3" t="s">
+        <v>66</v>
       </c>
       <c r="B49" s="4">
         <v>-5.5284000000000004</v>
@@ -11393,8 +11675,8 @@
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A50" s="3">
-        <v>1066</v>
+      <c r="A50" s="3" t="s">
+        <v>66</v>
       </c>
       <c r="B50" s="4">
         <v>-5.5284000000000004</v>
@@ -11437,8 +11719,8 @@
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A51" s="3">
-        <v>1066</v>
+      <c r="A51" s="3" t="s">
+        <v>66</v>
       </c>
       <c r="B51" s="4">
         <v>-5.5284000000000004</v>
@@ -11481,8 +11763,8 @@
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A52" s="3">
-        <v>1066</v>
+      <c r="A52" s="3" t="s">
+        <v>66</v>
       </c>
       <c r="B52" s="4">
         <v>-5.5284000000000004</v>
@@ -11525,8 +11807,8 @@
       </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A53" s="3">
-        <v>1066</v>
+      <c r="A53" s="3" t="s">
+        <v>66</v>
       </c>
       <c r="B53" s="4">
         <v>-5.5284000000000004</v>
@@ -11569,8 +11851,8 @@
       </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A54" s="3">
-        <v>1066</v>
+      <c r="A54" s="3" t="s">
+        <v>66</v>
       </c>
       <c r="B54" s="4">
         <v>-5.5284000000000004</v>
@@ -11613,8 +11895,8 @@
       </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A55" s="3">
-        <v>1066</v>
+      <c r="A55" s="3" t="s">
+        <v>66</v>
       </c>
       <c r="B55" s="4">
         <v>-5.5284000000000004</v>
@@ -11657,8 +11939,8 @@
       </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A56" s="3">
-        <v>1416</v>
+      <c r="A56" s="3" t="s">
+        <v>70</v>
       </c>
       <c r="B56" s="4">
         <v>-4.1619000000000002</v>
@@ -11701,8 +11983,8 @@
       </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A57" s="3">
-        <v>1416</v>
+      <c r="A57" s="3" t="s">
+        <v>70</v>
       </c>
       <c r="B57" s="4">
         <v>-4.1619000000000002</v>
@@ -11745,8 +12027,8 @@
       </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A58" s="3">
-        <v>1416</v>
+      <c r="A58" s="3" t="s">
+        <v>70</v>
       </c>
       <c r="B58" s="4">
         <v>-4.1619000000000002</v>
@@ -11789,8 +12071,8 @@
       </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A59" s="3">
-        <v>1416</v>
+      <c r="A59" s="3" t="s">
+        <v>70</v>
       </c>
       <c r="B59" s="4">
         <v>-4.1619000000000002</v>
@@ -11833,8 +12115,8 @@
       </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A60" s="3">
-        <v>1416</v>
+      <c r="A60" s="3" t="s">
+        <v>70</v>
       </c>
       <c r="B60" s="4">
         <v>-4.1619000000000002</v>
@@ -11877,8 +12159,8 @@
       </c>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A61" s="3">
-        <v>1416</v>
+      <c r="A61" s="3" t="s">
+        <v>70</v>
       </c>
       <c r="B61" s="4">
         <v>-4.1619000000000002</v>
@@ -11921,8 +12203,8 @@
       </c>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A62" s="3">
-        <v>1416</v>
+      <c r="A62" s="3" t="s">
+        <v>70</v>
       </c>
       <c r="B62" s="4">
         <v>-4.1619000000000002</v>
@@ -11965,8 +12247,8 @@
       </c>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A63" s="3">
-        <v>1416</v>
+      <c r="A63" s="3" t="s">
+        <v>70</v>
       </c>
       <c r="B63" s="4">
         <v>-4.1619000000000002</v>
@@ -12009,8 +12291,8 @@
       </c>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A64" s="3">
-        <v>1416</v>
+      <c r="A64" s="3" t="s">
+        <v>70</v>
       </c>
       <c r="B64" s="4">
         <v>-4.1619000000000002</v>
@@ -12053,8 +12335,8 @@
       </c>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A65" s="3">
-        <v>1416</v>
+      <c r="A65" s="3" t="s">
+        <v>70</v>
       </c>
       <c r="B65" s="4">
         <v>-4.1619000000000002</v>
@@ -12097,8 +12379,8 @@
       </c>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A66" s="3">
-        <v>1416</v>
+      <c r="A66" s="3" t="s">
+        <v>70</v>
       </c>
       <c r="B66" s="4">
         <v>-4.1619000000000002</v>
@@ -12141,8 +12423,8 @@
       </c>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A67" s="3">
-        <v>1437</v>
+      <c r="A67" s="3" t="s">
+        <v>71</v>
       </c>
       <c r="B67" s="4">
         <v>-14.242000000000001</v>
@@ -12185,8 +12467,8 @@
       </c>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A68" s="3">
-        <v>1437</v>
+      <c r="A68" s="3" t="s">
+        <v>71</v>
       </c>
       <c r="B68" s="4">
         <v>-14.242000000000001</v>
@@ -12229,8 +12511,8 @@
       </c>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A69" s="3">
-        <v>1437</v>
+      <c r="A69" s="3" t="s">
+        <v>71</v>
       </c>
       <c r="B69" s="4">
         <v>-14.242000000000001</v>
@@ -12273,8 +12555,8 @@
       </c>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A70" s="3">
-        <v>1437</v>
+      <c r="A70" s="3" t="s">
+        <v>71</v>
       </c>
       <c r="B70" s="4">
         <v>-14.242000000000001</v>
@@ -12317,8 +12599,8 @@
       </c>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A71" s="3">
-        <v>1437</v>
+      <c r="A71" s="3" t="s">
+        <v>71</v>
       </c>
       <c r="B71" s="4">
         <v>-14.242000000000001</v>
@@ -12361,8 +12643,8 @@
       </c>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A72" s="3">
-        <v>1437</v>
+      <c r="A72" s="3" t="s">
+        <v>71</v>
       </c>
       <c r="B72" s="4">
         <v>-14.242000000000001</v>
@@ -12405,8 +12687,8 @@
       </c>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A73" s="3">
-        <v>1437</v>
+      <c r="A73" s="3" t="s">
+        <v>71</v>
       </c>
       <c r="B73" s="4">
         <v>-14.242000000000001</v>
@@ -12449,8 +12731,8 @@
       </c>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A74" s="3">
-        <v>1437</v>
+      <c r="A74" s="3" t="s">
+        <v>71</v>
       </c>
       <c r="B74" s="4">
         <v>-14.242000000000001</v>
@@ -12493,8 +12775,8 @@
       </c>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A75" s="3">
-        <v>1492</v>
+      <c r="A75" s="3" t="s">
+        <v>72</v>
       </c>
       <c r="B75" s="4">
         <v>-12.973100000000001</v>
@@ -12537,8 +12819,8 @@
       </c>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A76" s="3">
-        <v>1492</v>
+      <c r="A76" s="3" t="s">
+        <v>72</v>
       </c>
       <c r="B76" s="4">
         <v>-12.973100000000001</v>
@@ -12581,8 +12863,8 @@
       </c>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A77" s="3">
-        <v>1492</v>
+      <c r="A77" s="3" t="s">
+        <v>72</v>
       </c>
       <c r="B77" s="4">
         <v>-12.973100000000001</v>
@@ -12625,8 +12907,8 @@
       </c>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A78" s="3">
-        <v>1492</v>
+      <c r="A78" s="3" t="s">
+        <v>72</v>
       </c>
       <c r="B78" s="4">
         <v>-12.973100000000001</v>
@@ -12669,8 +12951,8 @@
       </c>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A79" s="3">
-        <v>1492</v>
+      <c r="A79" s="3" t="s">
+        <v>72</v>
       </c>
       <c r="B79" s="4">
         <v>-12.973100000000001</v>
@@ -12713,8 +12995,8 @@
       </c>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A80" s="3">
-        <v>1492</v>
+      <c r="A80" s="3" t="s">
+        <v>72</v>
       </c>
       <c r="B80" s="4">
         <v>-12.973100000000001</v>
@@ -12757,8 +13039,8 @@
       </c>
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A81" s="3">
-        <v>1492</v>
+      <c r="A81" s="3" t="s">
+        <v>72</v>
       </c>
       <c r="B81" s="4">
         <v>-12.973100000000001</v>
@@ -12801,8 +13083,8 @@
       </c>
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A82" s="3">
-        <v>1492</v>
+      <c r="A82" s="3" t="s">
+        <v>72</v>
       </c>
       <c r="B82" s="4">
         <v>-12.973100000000001</v>
@@ -12845,8 +13127,8 @@
       </c>
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A83" s="3">
-        <v>1492</v>
+      <c r="A83" s="3" t="s">
+        <v>72</v>
       </c>
       <c r="B83" s="4">
         <v>-12.973100000000001</v>
@@ -12889,8 +13171,8 @@
       </c>
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A84" s="3">
-        <v>1492</v>
+      <c r="A84" s="3" t="s">
+        <v>72</v>
       </c>
       <c r="B84" s="4">
         <v>-12.973100000000001</v>
@@ -12933,8 +13215,8 @@
       </c>
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A85" s="3">
-        <v>1492</v>
+      <c r="A85" s="3" t="s">
+        <v>72</v>
       </c>
       <c r="B85" s="4">
         <v>-12.973100000000001</v>
@@ -12977,8 +13259,8 @@
       </c>
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A86" s="3">
-        <v>1492</v>
+      <c r="A86" s="3" t="s">
+        <v>72</v>
       </c>
       <c r="B86" s="4">
         <v>-12.973100000000001</v>
@@ -13021,8 +13303,8 @@
       </c>
     </row>
     <row r="87" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A87" s="3">
-        <v>2165</v>
+      <c r="A87" s="5" t="s">
+        <v>118</v>
       </c>
       <c r="B87" s="4">
         <v>-8.6591000000000005</v>
@@ -13065,8 +13347,8 @@
       </c>
     </row>
     <row r="88" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A88" s="3">
-        <v>2165</v>
+      <c r="A88" s="5" t="s">
+        <v>118</v>
       </c>
       <c r="B88" s="4">
         <v>-8.6591000000000005</v>
@@ -13109,8 +13391,8 @@
       </c>
     </row>
     <row r="89" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A89" s="3">
-        <v>2165</v>
+      <c r="A89" s="5" t="s">
+        <v>118</v>
       </c>
       <c r="B89" s="4">
         <v>-8.6591000000000005</v>
@@ -13153,8 +13435,8 @@
       </c>
     </row>
     <row r="90" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A90" s="3">
-        <v>2165</v>
+      <c r="A90" s="5" t="s">
+        <v>118</v>
       </c>
       <c r="B90" s="4">
         <v>-8.6591000000000005</v>
@@ -13197,8 +13479,8 @@
       </c>
     </row>
     <row r="91" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A91" s="3">
-        <v>2165</v>
+      <c r="A91" s="5" t="s">
+        <v>118</v>
       </c>
       <c r="B91" s="4">
         <v>-8.6591000000000005</v>
@@ -13241,8 +13523,8 @@
       </c>
     </row>
     <row r="92" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A92" s="3">
-        <v>2165</v>
+      <c r="A92" s="5" t="s">
+        <v>118</v>
       </c>
       <c r="B92" s="4">
         <v>-8.6591000000000005</v>
@@ -13285,8 +13567,8 @@
       </c>
     </row>
     <row r="93" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A93" s="3">
-        <v>2182</v>
+      <c r="A93" s="5" t="s">
+        <v>94</v>
       </c>
       <c r="B93" s="4">
         <v>-22.052700000000002</v>
@@ -13329,8 +13611,8 @@
       </c>
     </row>
     <row r="94" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A94" s="3">
-        <v>2182</v>
+      <c r="A94" s="5" t="s">
+        <v>94</v>
       </c>
       <c r="B94" s="4">
         <v>-22.052700000000002</v>
@@ -13373,8 +13655,8 @@
       </c>
     </row>
     <row r="95" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A95" s="3">
-        <v>2182</v>
+      <c r="A95" s="5" t="s">
+        <v>94</v>
       </c>
       <c r="B95" s="4">
         <v>-22.052700000000002</v>
@@ -13417,8 +13699,8 @@
       </c>
     </row>
     <row r="96" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A96" s="3">
-        <v>2182</v>
+      <c r="A96" s="5" t="s">
+        <v>94</v>
       </c>
       <c r="B96" s="4">
         <v>-22.052700000000002</v>
@@ -13461,8 +13743,8 @@
       </c>
     </row>
     <row r="97" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A97" s="3">
-        <v>2182</v>
+      <c r="A97" s="5" t="s">
+        <v>94</v>
       </c>
       <c r="B97" s="4">
         <v>-22.052700000000002</v>
@@ -13505,8 +13787,8 @@
       </c>
     </row>
     <row r="98" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A98" s="3">
-        <v>2182</v>
+      <c r="A98" s="5" t="s">
+        <v>94</v>
       </c>
       <c r="B98" s="4">
         <v>-22.052700000000002</v>
@@ -13549,8 +13831,8 @@
       </c>
     </row>
     <row r="99" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A99" s="3">
-        <v>2182</v>
+      <c r="A99" s="5" t="s">
+        <v>94</v>
       </c>
       <c r="B99" s="4">
         <v>-22.052700000000002</v>
@@ -13593,8 +13875,8 @@
       </c>
     </row>
     <row r="100" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A100" s="3">
-        <v>2182</v>
+      <c r="A100" s="5" t="s">
+        <v>94</v>
       </c>
       <c r="B100" s="4">
         <v>-22.052700000000002</v>
@@ -13637,8 +13919,8 @@
       </c>
     </row>
     <row r="101" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A101" s="3">
-        <v>2182</v>
+      <c r="A101" s="5" t="s">
+        <v>94</v>
       </c>
       <c r="B101" s="4">
         <v>-22.052700000000002</v>
@@ -13681,8 +13963,8 @@
       </c>
     </row>
     <row r="102" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A102" s="3">
-        <v>2182</v>
+      <c r="A102" s="5" t="s">
+        <v>94</v>
       </c>
       <c r="B102" s="4">
         <v>-22.052700000000002</v>
@@ -13725,8 +14007,8 @@
       </c>
     </row>
     <row r="103" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A103" s="3">
-        <v>2182</v>
+      <c r="A103" s="5" t="s">
+        <v>94</v>
       </c>
       <c r="B103" s="4">
         <v>-22.052700000000002</v>
@@ -13769,8 +14051,8 @@
       </c>
     </row>
     <row r="104" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A104" s="3">
-        <v>2182</v>
+      <c r="A104" s="5" t="s">
+        <v>94</v>
       </c>
       <c r="B104" s="4">
         <v>-22.052700000000002</v>
@@ -13813,8 +14095,8 @@
       </c>
     </row>
     <row r="105" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A105" s="3">
-        <v>2182</v>
+      <c r="A105" s="5" t="s">
+        <v>94</v>
       </c>
       <c r="B105" s="4">
         <v>-22.052700000000002</v>
@@ -13857,8 +14139,8 @@
       </c>
     </row>
     <row r="106" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A106" s="3">
-        <v>1884</v>
+      <c r="A106" s="3" t="s">
+        <v>79</v>
       </c>
       <c r="B106" s="4">
         <v>-15.0342</v>
@@ -13901,8 +14183,8 @@
       </c>
     </row>
     <row r="107" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A107" s="3">
-        <v>1884</v>
+      <c r="A107" s="3" t="s">
+        <v>79</v>
       </c>
       <c r="B107" s="4">
         <v>-15.0342</v>
@@ -13945,8 +14227,8 @@
       </c>
     </row>
     <row r="108" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A108" s="3">
-        <v>1884</v>
+      <c r="A108" s="3" t="s">
+        <v>79</v>
       </c>
       <c r="B108" s="4">
         <v>-15.0342</v>
@@ -13989,8 +14271,8 @@
       </c>
     </row>
     <row r="109" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A109" s="3">
-        <v>1884</v>
+      <c r="A109" s="3" t="s">
+        <v>79</v>
       </c>
       <c r="B109" s="4">
         <v>-15.0342</v>
@@ -14033,8 +14315,8 @@
       </c>
     </row>
     <row r="110" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A110" s="3">
-        <v>1884</v>
+      <c r="A110" s="3" t="s">
+        <v>79</v>
       </c>
       <c r="B110" s="4">
         <v>-15.0342</v>
@@ -14077,8 +14359,8 @@
       </c>
     </row>
     <row r="111" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A111" s="3">
-        <v>1884</v>
+      <c r="A111" s="3" t="s">
+        <v>79</v>
       </c>
       <c r="B111" s="4">
         <v>-15.0342</v>
@@ -14121,8 +14403,8 @@
       </c>
     </row>
     <row r="112" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A112" s="3">
-        <v>1884</v>
+      <c r="A112" s="3" t="s">
+        <v>79</v>
       </c>
       <c r="B112" s="4">
         <v>-15.0342</v>
@@ -14165,8 +14447,8 @@
       </c>
     </row>
     <row r="113" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A113" s="3">
-        <v>1951</v>
+      <c r="A113" s="5" t="s">
+        <v>89</v>
       </c>
       <c r="B113" s="4">
         <v>-4.7603999999999997</v>
@@ -14209,8 +14491,8 @@
       </c>
     </row>
     <row r="114" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A114" s="3">
-        <v>1951</v>
+      <c r="A114" s="5" t="s">
+        <v>89</v>
       </c>
       <c r="B114" s="4">
         <v>-4.7603999999999997</v>
@@ -14253,8 +14535,8 @@
       </c>
     </row>
     <row r="115" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A115" s="3">
-        <v>1951</v>
+      <c r="A115" s="5" t="s">
+        <v>89</v>
       </c>
       <c r="B115" s="4">
         <v>-4.7603999999999997</v>
@@ -14297,8 +14579,8 @@
       </c>
     </row>
     <row r="116" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A116" s="3">
-        <v>1951</v>
+      <c r="A116" s="5" t="s">
+        <v>89</v>
       </c>
       <c r="B116" s="4">
         <v>-4.7603999999999997</v>
@@ -14341,8 +14623,8 @@
       </c>
     </row>
     <row r="117" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A117" s="3">
-        <v>1951</v>
+      <c r="A117" s="5" t="s">
+        <v>89</v>
       </c>
       <c r="B117" s="4">
         <v>-4.7603999999999997</v>
@@ -14385,8 +14667,8 @@
       </c>
     </row>
     <row r="118" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A118" s="3">
-        <v>1951</v>
+      <c r="A118" s="5" t="s">
+        <v>89</v>
       </c>
       <c r="B118" s="4">
         <v>-4.7603999999999997</v>
@@ -14429,8 +14711,8 @@
       </c>
     </row>
     <row r="119" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A119" s="3">
-        <v>1951</v>
+      <c r="A119" s="5" t="s">
+        <v>89</v>
       </c>
       <c r="B119" s="4">
         <v>-4.7603999999999997</v>
@@ -14473,8 +14755,8 @@
       </c>
     </row>
     <row r="120" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A120" s="3">
-        <v>2001</v>
+      <c r="A120" s="5" t="s">
+        <v>90</v>
       </c>
       <c r="B120" s="4">
         <v>16.264700000000001</v>
@@ -14517,8 +14799,8 @@
       </c>
     </row>
     <row r="121" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A121" s="3">
-        <v>2001</v>
+      <c r="A121" s="5" t="s">
+        <v>90</v>
       </c>
       <c r="B121" s="4">
         <v>16.264700000000001</v>
@@ -14561,8 +14843,8 @@
       </c>
     </row>
     <row r="122" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A122" s="3">
-        <v>2001</v>
+      <c r="A122" s="5" t="s">
+        <v>90</v>
       </c>
       <c r="B122" s="4">
         <v>16.264700000000001</v>
@@ -14605,8 +14887,8 @@
       </c>
     </row>
     <row r="123" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A123" s="3">
-        <v>2001</v>
+      <c r="A123" s="5" t="s">
+        <v>90</v>
       </c>
       <c r="B123" s="4">
         <v>16.264700000000001</v>
@@ -14649,8 +14931,8 @@
       </c>
     </row>
     <row r="124" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A124" s="3">
-        <v>2004</v>
+      <c r="A124" s="5" t="s">
+        <v>91</v>
       </c>
       <c r="B124" s="4">
         <v>-16.2209</v>
@@ -14693,8 +14975,8 @@
       </c>
     </row>
     <row r="125" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A125" s="3">
-        <v>2004</v>
+      <c r="A125" s="5" t="s">
+        <v>91</v>
       </c>
       <c r="B125" s="4">
         <v>-16.2209</v>
@@ -14737,8 +15019,8 @@
       </c>
     </row>
     <row r="126" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A126" s="3">
-        <v>2004</v>
+      <c r="A126" s="5" t="s">
+        <v>91</v>
       </c>
       <c r="B126" s="4">
         <v>-16.2209</v>
@@ -14781,8 +15063,8 @@
       </c>
     </row>
     <row r="127" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A127" s="3">
-        <v>2004</v>
+      <c r="A127" s="5" t="s">
+        <v>91</v>
       </c>
       <c r="B127" s="4">
         <v>-16.2209</v>
@@ -14825,8 +15107,8 @@
       </c>
     </row>
     <row r="128" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A128" s="3">
-        <v>2004</v>
+      <c r="A128" s="5" t="s">
+        <v>91</v>
       </c>
       <c r="B128" s="4">
         <v>-16.2209</v>
@@ -14869,8 +15151,8 @@
       </c>
     </row>
     <row r="129" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A129" s="3">
-        <v>2004</v>
+      <c r="A129" s="5" t="s">
+        <v>91</v>
       </c>
       <c r="B129" s="4">
         <v>-16.2209</v>
@@ -14913,8 +15195,8 @@
       </c>
     </row>
     <row r="130" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A130" s="3">
-        <v>2004</v>
+      <c r="A130" s="5" t="s">
+        <v>91</v>
       </c>
       <c r="B130" s="4">
         <v>-16.2209</v>
@@ -14957,8 +15239,8 @@
       </c>
     </row>
     <row r="131" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A131" s="3">
-        <v>2004</v>
+      <c r="A131" s="5" t="s">
+        <v>91</v>
       </c>
       <c r="B131" s="4">
         <v>-16.2209</v>
@@ -15001,8 +15283,8 @@
       </c>
     </row>
     <row r="132" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A132" s="3">
-        <v>2004</v>
+      <c r="A132" s="5" t="s">
+        <v>91</v>
       </c>
       <c r="B132" s="4">
         <v>-16.2209</v>
@@ -15045,8 +15327,8 @@
       </c>
     </row>
     <row r="133" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A133" s="3">
-        <v>2164</v>
+      <c r="A133" s="5" t="s">
+        <v>93</v>
       </c>
       <c r="B133" s="4">
         <v>19.946100000000001</v>
@@ -15089,8 +15371,8 @@
       </c>
     </row>
     <row r="134" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A134" s="3">
-        <v>2164</v>
+      <c r="A134" s="5" t="s">
+        <v>93</v>
       </c>
       <c r="B134" s="4">
         <v>19.946100000000001</v>
@@ -15133,8 +15415,8 @@
       </c>
     </row>
     <row r="135" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A135" s="3">
-        <v>2164</v>
+      <c r="A135" s="5" t="s">
+        <v>93</v>
       </c>
       <c r="B135" s="4">
         <v>19.946100000000001</v>
@@ -15177,8 +15459,8 @@
       </c>
     </row>
     <row r="136" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A136" s="3">
-        <v>2164</v>
+      <c r="A136" s="5" t="s">
+        <v>93</v>
       </c>
       <c r="B136" s="4">
         <v>19.946100000000001</v>
@@ -15221,8 +15503,8 @@
       </c>
     </row>
     <row r="137" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A137" s="3">
-        <v>2164</v>
+      <c r="A137" s="5" t="s">
+        <v>93</v>
       </c>
       <c r="B137" s="4">
         <v>19.946100000000001</v>
@@ -15265,8 +15547,8 @@
       </c>
     </row>
     <row r="138" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A138" s="3">
-        <v>2164</v>
+      <c r="A138" s="5" t="s">
+        <v>93</v>
       </c>
       <c r="B138" s="4">
         <v>19.946100000000001</v>
@@ -15309,8 +15591,8 @@
       </c>
     </row>
     <row r="139" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A139" s="3">
-        <v>4386</v>
+      <c r="A139" s="5" t="s">
+        <v>112</v>
       </c>
       <c r="B139" s="4">
         <v>-8.1184999999999992</v>
@@ -15353,8 +15635,8 @@
       </c>
     </row>
     <row r="140" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A140" s="3">
-        <v>4386</v>
+      <c r="A140" s="5" t="s">
+        <v>112</v>
       </c>
       <c r="B140" s="4">
         <v>-8.1184999999999992</v>
@@ -15397,8 +15679,8 @@
       </c>
     </row>
     <row r="141" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A141" s="3">
-        <v>4386</v>
+      <c r="A141" s="5" t="s">
+        <v>112</v>
       </c>
       <c r="B141" s="4">
         <v>-8.1184999999999992</v>
@@ -15441,8 +15723,8 @@
       </c>
     </row>
     <row r="142" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A142" s="3">
-        <v>4386</v>
+      <c r="A142" s="5" t="s">
+        <v>112</v>
       </c>
       <c r="B142" s="4">
         <v>-8.1184999999999992</v>
@@ -15485,8 +15767,8 @@
       </c>
     </row>
     <row r="143" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A143" s="3">
-        <v>4386</v>
+      <c r="A143" s="5" t="s">
+        <v>112</v>
       </c>
       <c r="B143" s="4">
         <v>-8.1184999999999992</v>
@@ -15529,8 +15811,8 @@
       </c>
     </row>
     <row r="144" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A144" s="3">
-        <v>4386</v>
+      <c r="A144" s="5" t="s">
+        <v>112</v>
       </c>
       <c r="B144" s="4">
         <v>-8.1184999999999992</v>
@@ -15573,8 +15855,8 @@
       </c>
     </row>
     <row r="145" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A145" s="3">
-        <v>4386</v>
+      <c r="A145" s="5" t="s">
+        <v>112</v>
       </c>
       <c r="B145" s="4">
         <v>-8.1184999999999992</v>
@@ -15617,8 +15899,8 @@
       </c>
     </row>
     <row r="146" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A146" s="3">
-        <v>4460</v>
+      <c r="A146" s="5" t="s">
+        <v>113</v>
       </c>
       <c r="B146" s="4">
         <v>-29.5747</v>
@@ -15661,8 +15943,8 @@
       </c>
     </row>
     <row r="147" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A147" s="3">
-        <v>4460</v>
+      <c r="A147" s="5" t="s">
+        <v>113</v>
       </c>
       <c r="B147" s="4">
         <v>-29.5747</v>
@@ -15705,8 +15987,8 @@
       </c>
     </row>
     <row r="148" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A148" s="3">
-        <v>4460</v>
+      <c r="A148" s="5" t="s">
+        <v>113</v>
       </c>
       <c r="B148" s="4">
         <v>-29.5747</v>
@@ -15749,8 +16031,8 @@
       </c>
     </row>
     <row r="149" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A149" s="3">
-        <v>4460</v>
+      <c r="A149" s="5" t="s">
+        <v>113</v>
       </c>
       <c r="B149" s="4">
         <v>-29.5747</v>
@@ -15793,8 +16075,8 @@
       </c>
     </row>
     <row r="150" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A150" s="3">
-        <v>4460</v>
+      <c r="A150" s="5" t="s">
+        <v>113</v>
       </c>
       <c r="B150" s="4">
         <v>-29.5747</v>
@@ -15837,8 +16119,8 @@
       </c>
     </row>
     <row r="151" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A151" s="3">
-        <v>4460</v>
+      <c r="A151" s="5" t="s">
+        <v>113</v>
       </c>
       <c r="B151" s="4">
         <v>-29.5747</v>
@@ -15881,8 +16163,8 @@
       </c>
     </row>
     <row r="152" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A152" s="3">
-        <v>4460</v>
+      <c r="A152" s="5" t="s">
+        <v>113</v>
       </c>
       <c r="B152" s="4">
         <v>-29.5747</v>
@@ -15925,8 +16207,8 @@
       </c>
     </row>
     <row r="153" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A153" s="3">
-        <v>4460</v>
+      <c r="A153" s="5" t="s">
+        <v>113</v>
       </c>
       <c r="B153" s="4">
         <v>-29.5747</v>
@@ -15969,8 +16251,8 @@
       </c>
     </row>
     <row r="154" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A154" s="3">
-        <v>4604</v>
+      <c r="A154" s="5" t="s">
+        <v>114</v>
       </c>
       <c r="B154" s="4">
         <v>-11.6229</v>
@@ -16013,8 +16295,8 @@
       </c>
     </row>
     <row r="155" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A155" s="3">
-        <v>4604</v>
+      <c r="A155" s="5" t="s">
+        <v>114</v>
       </c>
       <c r="B155" s="4">
         <v>-11.6229</v>
@@ -16057,8 +16339,8 @@
       </c>
     </row>
     <row r="156" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A156" s="3">
-        <v>4604</v>
+      <c r="A156" s="5" t="s">
+        <v>114</v>
       </c>
       <c r="B156" s="4">
         <v>-11.6229</v>
@@ -16101,8 +16383,8 @@
       </c>
     </row>
     <row r="157" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A157" s="3">
-        <v>4604</v>
+      <c r="A157" s="5" t="s">
+        <v>114</v>
       </c>
       <c r="B157" s="4">
         <v>-11.6229</v>
@@ -16145,8 +16427,8 @@
       </c>
     </row>
     <row r="158" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A158" s="3">
-        <v>4604</v>
+      <c r="A158" s="5" t="s">
+        <v>114</v>
       </c>
       <c r="B158" s="4">
         <v>-11.6229</v>
@@ -16189,8 +16471,8 @@
       </c>
     </row>
     <row r="159" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A159" s="3">
-        <v>4604</v>
+      <c r="A159" s="5" t="s">
+        <v>114</v>
       </c>
       <c r="B159" s="4">
         <v>-11.6229</v>
@@ -16233,8 +16515,8 @@
       </c>
     </row>
     <row r="160" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A160" s="3">
-        <v>4604</v>
+      <c r="A160" s="5" t="s">
+        <v>114</v>
       </c>
       <c r="B160" s="4">
         <v>-11.6229</v>
@@ -16277,8 +16559,8 @@
       </c>
     </row>
     <row r="161" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A161" s="3">
-        <v>4604</v>
+      <c r="A161" s="5" t="s">
+        <v>114</v>
       </c>
       <c r="B161" s="4">
         <v>-11.6229</v>
@@ -16321,8 +16603,8 @@
       </c>
     </row>
     <row r="162" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A162" s="3">
-        <v>4604</v>
+      <c r="A162" s="5" t="s">
+        <v>114</v>
       </c>
       <c r="B162" s="4">
         <v>-11.6229</v>
@@ -16365,8 +16647,8 @@
       </c>
     </row>
     <row r="163" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A163" s="3">
-        <v>4604</v>
+      <c r="A163" s="5" t="s">
+        <v>114</v>
       </c>
       <c r="B163" s="4">
         <v>-11.6229</v>
@@ -16409,8 +16691,8 @@
       </c>
     </row>
     <row r="164" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A164" s="3">
-        <v>4604</v>
+      <c r="A164" s="5" t="s">
+        <v>114</v>
       </c>
       <c r="B164" s="4">
         <v>-11.6229</v>
@@ -16453,8 +16735,8 @@
       </c>
     </row>
     <row r="165" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A165" s="3">
-        <v>4604</v>
+      <c r="A165" s="5" t="s">
+        <v>114</v>
       </c>
       <c r="B165" s="4">
         <v>-11.6229</v>
@@ -16497,8 +16779,8 @@
       </c>
     </row>
     <row r="166" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A166" s="3">
-        <v>4604</v>
+      <c r="A166" s="5" t="s">
+        <v>114</v>
       </c>
       <c r="B166" s="4">
         <v>-11.6229</v>
@@ -16541,8 +16823,8 @@
       </c>
     </row>
     <row r="167" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A167" s="3">
-        <v>4604</v>
+      <c r="A167" s="5" t="s">
+        <v>114</v>
       </c>
       <c r="B167" s="4">
         <v>-11.6229</v>
@@ -16585,8 +16867,8 @@
       </c>
     </row>
     <row r="168" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A168" s="3">
-        <v>4604</v>
+      <c r="A168" s="5" t="s">
+        <v>114</v>
       </c>
       <c r="B168" s="4">
         <v>-11.6229</v>
@@ -16629,8 +16911,8 @@
       </c>
     </row>
     <row r="169" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A169" s="3">
-        <v>4604</v>
+      <c r="A169" s="5" t="s">
+        <v>114</v>
       </c>
       <c r="B169" s="4">
         <v>-11.6229</v>
@@ -16673,8 +16955,8 @@
       </c>
     </row>
     <row r="170" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A170" s="3">
-        <v>4604</v>
+      <c r="A170" s="5" t="s">
+        <v>114</v>
       </c>
       <c r="B170" s="4">
         <v>-11.6229</v>
@@ -16717,8 +16999,8 @@
       </c>
     </row>
     <row r="171" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A171" s="3">
-        <v>4604</v>
+      <c r="A171" s="5" t="s">
+        <v>114</v>
       </c>
       <c r="B171" s="4">
         <v>-11.6229</v>
@@ -16761,8 +17043,8 @@
       </c>
     </row>
     <row r="172" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A172" s="3">
-        <v>4604</v>
+      <c r="A172" s="5" t="s">
+        <v>114</v>
       </c>
       <c r="B172" s="4">
         <v>-11.6229</v>
@@ -16805,8 +17087,8 @@
       </c>
     </row>
     <row r="173" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A173" s="3">
-        <v>4604</v>
+      <c r="A173" s="5" t="s">
+        <v>114</v>
       </c>
       <c r="B173" s="4">
         <v>-11.6229</v>
@@ -16849,8 +17131,8 @@
       </c>
     </row>
     <row r="174" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A174" s="3">
-        <v>4604</v>
+      <c r="A174" s="5" t="s">
+        <v>114</v>
       </c>
       <c r="B174" s="4">
         <v>-11.6229</v>
@@ -16893,8 +17175,8 @@
       </c>
     </row>
     <row r="175" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A175" s="3">
-        <v>4604</v>
+      <c r="A175" s="5" t="s">
+        <v>114</v>
       </c>
       <c r="B175" s="4">
         <v>-11.6229</v>
@@ -16937,8 +17219,8 @@
       </c>
     </row>
     <row r="176" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A176" s="3">
-        <v>4604</v>
+      <c r="A176" s="5" t="s">
+        <v>114</v>
       </c>
       <c r="B176" s="4">
         <v>-11.6229</v>
@@ -16981,8 +17263,8 @@
       </c>
     </row>
     <row r="177" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A177" s="3">
-        <v>4604</v>
+      <c r="A177" s="5" t="s">
+        <v>114</v>
       </c>
       <c r="B177" s="4">
         <v>-11.6229</v>
@@ -17025,8 +17307,8 @@
       </c>
     </row>
     <row r="178" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A178" s="3">
-        <v>4604</v>
+      <c r="A178" s="5" t="s">
+        <v>114</v>
       </c>
       <c r="B178" s="4">
         <v>-11.6229</v>
@@ -17069,8 +17351,8 @@
       </c>
     </row>
     <row r="179" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A179" s="3">
-        <v>4604</v>
+      <c r="A179" s="5" t="s">
+        <v>114</v>
       </c>
       <c r="B179" s="4">
         <v>-11.6229</v>
@@ -17113,8 +17395,8 @@
       </c>
     </row>
     <row r="180" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A180" s="3">
-        <v>3971</v>
+      <c r="A180" s="5" t="s">
+        <v>110</v>
       </c>
       <c r="B180" s="4">
         <v>-27.8413</v>
@@ -17157,8 +17439,8 @@
       </c>
     </row>
     <row r="181" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A181" s="3">
-        <v>3971</v>
+      <c r="A181" s="5" t="s">
+        <v>110</v>
       </c>
       <c r="B181" s="4">
         <v>-27.8413</v>
@@ -17201,8 +17483,8 @@
       </c>
     </row>
     <row r="182" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A182" s="3">
-        <v>3971</v>
+      <c r="A182" s="5" t="s">
+        <v>110</v>
       </c>
       <c r="B182" s="4">
         <v>-27.8413</v>
@@ -17245,8 +17527,8 @@
       </c>
     </row>
     <row r="183" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A183" s="3">
-        <v>3971</v>
+      <c r="A183" s="5" t="s">
+        <v>110</v>
       </c>
       <c r="B183" s="4">
         <v>-27.8413</v>
@@ -17289,8 +17571,8 @@
       </c>
     </row>
     <row r="184" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A184" s="3">
-        <v>3971</v>
+      <c r="A184" s="5" t="s">
+        <v>110</v>
       </c>
       <c r="B184" s="4">
         <v>-27.8413</v>
@@ -17333,8 +17615,8 @@
       </c>
     </row>
     <row r="185" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A185" s="3">
-        <v>3971</v>
+      <c r="A185" s="5" t="s">
+        <v>110</v>
       </c>
       <c r="B185" s="4">
         <v>-27.8413</v>
@@ -17377,8 +17659,8 @@
       </c>
     </row>
     <row r="186" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A186" s="3">
-        <v>3971</v>
+      <c r="A186" s="5" t="s">
+        <v>110</v>
       </c>
       <c r="B186" s="4">
         <v>-27.8413</v>
@@ -17421,8 +17703,8 @@
       </c>
     </row>
     <row r="187" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A187" s="3">
-        <v>494</v>
+      <c r="A187" s="3" t="s">
+        <v>65</v>
       </c>
       <c r="B187" s="4">
         <v>-24.995200000000001</v>
@@ -17465,8 +17747,8 @@
       </c>
     </row>
     <row r="188" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A188" s="3">
-        <v>494</v>
+      <c r="A188" s="3" t="s">
+        <v>65</v>
       </c>
       <c r="B188" s="4">
         <v>-24.995200000000001</v>
@@ -17509,8 +17791,8 @@
       </c>
     </row>
     <row r="189" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A189" s="3">
-        <v>494</v>
+      <c r="A189" s="3" t="s">
+        <v>65</v>
       </c>
       <c r="B189" s="4">
         <v>-24.995200000000001</v>
@@ -17553,8 +17835,8 @@
       </c>
     </row>
     <row r="190" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A190" s="3">
-        <v>494</v>
+      <c r="A190" s="3" t="s">
+        <v>65</v>
       </c>
       <c r="B190" s="4">
         <v>-24.995200000000001</v>
@@ -17597,8 +17879,8 @@
       </c>
     </row>
     <row r="191" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A191" s="3">
-        <v>494</v>
+      <c r="A191" s="3" t="s">
+        <v>65</v>
       </c>
       <c r="B191" s="4">
         <v>-24.995200000000001</v>
@@ -17641,8 +17923,8 @@
       </c>
     </row>
     <row r="192" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A192" s="3">
-        <v>636</v>
+      <c r="A192" s="3" t="s">
+        <v>83</v>
       </c>
       <c r="B192" s="4">
         <v>12.879099999999999</v>
@@ -17685,8 +17967,8 @@
       </c>
     </row>
     <row r="193" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A193" s="3">
-        <v>636</v>
+      <c r="A193" s="3" t="s">
+        <v>83</v>
       </c>
       <c r="B193" s="4">
         <v>12.879099999999999</v>
@@ -17729,8 +18011,8 @@
       </c>
     </row>
     <row r="194" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A194" s="3">
-        <v>636</v>
+      <c r="A194" s="3" t="s">
+        <v>83</v>
       </c>
       <c r="B194" s="4">
         <v>12.879099999999999</v>
@@ -17773,8 +18055,8 @@
       </c>
     </row>
     <row r="195" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A195" s="3">
-        <v>636</v>
+      <c r="A195" s="3" t="s">
+        <v>83</v>
       </c>
       <c r="B195" s="4">
         <v>12.879099999999999</v>
@@ -17817,8 +18099,8 @@
       </c>
     </row>
     <row r="196" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A196" s="3">
-        <v>636</v>
+      <c r="A196" s="3" t="s">
+        <v>83</v>
       </c>
       <c r="B196" s="4">
         <v>12.879099999999999</v>
@@ -17861,8 +18143,8 @@
       </c>
     </row>
     <row r="197" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A197" s="3">
-        <v>636</v>
+      <c r="A197" s="3" t="s">
+        <v>83</v>
       </c>
       <c r="B197" s="4">
         <v>12.879099999999999</v>
@@ -17905,8 +18187,8 @@
       </c>
     </row>
     <row r="198" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A198" s="3">
-        <v>636</v>
+      <c r="A198" s="3" t="s">
+        <v>83</v>
       </c>
       <c r="B198" s="4">
         <v>12.879099999999999</v>
@@ -17949,8 +18231,8 @@
       </c>
     </row>
     <row r="199" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A199" s="3">
-        <v>636</v>
+      <c r="A199" s="3" t="s">
+        <v>83</v>
       </c>
       <c r="B199" s="4">
         <v>12.879099999999999</v>
@@ -17993,8 +18275,8 @@
       </c>
     </row>
     <row r="200" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A200" s="3">
-        <v>636</v>
+      <c r="A200" s="3" t="s">
+        <v>83</v>
       </c>
       <c r="B200" s="4">
         <v>12.879099999999999</v>
@@ -18037,8 +18319,8 @@
       </c>
     </row>
     <row r="201" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A201" s="3">
-        <v>645</v>
+      <c r="A201" s="3" t="s">
+        <v>84</v>
       </c>
       <c r="B201" s="4">
         <v>7.0168999999999997</v>
@@ -18081,8 +18363,8 @@
       </c>
     </row>
     <row r="202" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A202" s="3">
-        <v>645</v>
+      <c r="A202" s="3" t="s">
+        <v>84</v>
       </c>
       <c r="B202" s="4">
         <v>7.0168999999999997</v>
@@ -18125,8 +18407,8 @@
       </c>
     </row>
     <row r="203" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A203" s="3">
-        <v>645</v>
+      <c r="A203" s="3" t="s">
+        <v>84</v>
       </c>
       <c r="B203" s="4">
         <v>7.0168999999999997</v>
@@ -18169,8 +18451,8 @@
       </c>
     </row>
     <row r="204" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A204" s="3">
-        <v>1318</v>
+      <c r="A204" s="3" t="s">
+        <v>69</v>
       </c>
       <c r="B204" s="4">
         <v>13.6013</v>
@@ -18213,8 +18495,8 @@
       </c>
     </row>
     <row r="205" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A205" s="3">
-        <v>1318</v>
+      <c r="A205" s="3" t="s">
+        <v>69</v>
       </c>
       <c r="B205" s="4">
         <v>13.6013</v>
@@ -18257,8 +18539,8 @@
       </c>
     </row>
     <row r="206" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A206" s="3">
-        <v>1318</v>
+      <c r="A206" s="3" t="s">
+        <v>69</v>
       </c>
       <c r="B206" s="4">
         <v>13.6013</v>
@@ -18301,8 +18583,8 @@
       </c>
     </row>
     <row r="207" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A207" s="3">
-        <v>1318</v>
+      <c r="A207" s="3" t="s">
+        <v>69</v>
       </c>
       <c r="B207" s="4">
         <v>13.6013</v>
@@ -18345,8 +18627,8 @@
       </c>
     </row>
     <row r="208" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A208" s="3">
-        <v>1318</v>
+      <c r="A208" s="3" t="s">
+        <v>69</v>
       </c>
       <c r="B208" s="4">
         <v>13.6013</v>
@@ -18389,8 +18671,8 @@
       </c>
     </row>
     <row r="209" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A209" s="3">
-        <v>1318</v>
+      <c r="A209" s="3" t="s">
+        <v>69</v>
       </c>
       <c r="B209" s="4">
         <v>13.6013</v>
@@ -18433,8 +18715,8 @@
       </c>
     </row>
     <row r="210" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A210" s="3">
-        <v>1318</v>
+      <c r="A210" s="3" t="s">
+        <v>69</v>
       </c>
       <c r="B210" s="4">
         <v>13.6013</v>
@@ -18477,8 +18759,8 @@
       </c>
     </row>
     <row r="211" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A211" s="3">
-        <v>1318</v>
+      <c r="A211" s="3" t="s">
+        <v>69</v>
       </c>
       <c r="B211" s="4">
         <v>13.6013</v>
@@ -18521,8 +18803,8 @@
       </c>
     </row>
     <row r="212" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A212" s="3">
-        <v>1318</v>
+      <c r="A212" s="3" t="s">
+        <v>69</v>
       </c>
       <c r="B212" s="4">
         <v>13.6013</v>
@@ -18565,8 +18847,8 @@
       </c>
     </row>
     <row r="213" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A213" s="3">
-        <v>1547</v>
+      <c r="A213" s="3" t="s">
+        <v>73</v>
       </c>
       <c r="B213" s="4">
         <v>-52.887999999999998</v>
@@ -18609,8 +18891,8 @@
       </c>
     </row>
     <row r="214" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A214" s="3">
-        <v>1547</v>
+      <c r="A214" s="3" t="s">
+        <v>73</v>
       </c>
       <c r="B214" s="4">
         <v>-52.887999999999998</v>
@@ -18653,8 +18935,8 @@
       </c>
     </row>
     <row r="215" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A215" s="3">
-        <v>1547</v>
+      <c r="A215" s="3" t="s">
+        <v>73</v>
       </c>
       <c r="B215" s="4">
         <v>-52.887999999999998</v>
@@ -18697,8 +18979,8 @@
       </c>
     </row>
     <row r="216" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A216" s="3">
-        <v>1547</v>
+      <c r="A216" s="3" t="s">
+        <v>73</v>
       </c>
       <c r="B216" s="4">
         <v>-52.887999999999998</v>
@@ -18741,8 +19023,8 @@
       </c>
     </row>
     <row r="217" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A217" s="3">
-        <v>1547</v>
+      <c r="A217" s="3" t="s">
+        <v>73</v>
       </c>
       <c r="B217" s="4">
         <v>-52.887999999999998</v>
@@ -18785,8 +19067,8 @@
       </c>
     </row>
     <row r="218" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A218" s="3">
-        <v>1547</v>
+      <c r="A218" s="3" t="s">
+        <v>73</v>
       </c>
       <c r="B218" s="4">
         <v>-52.887999999999998</v>
@@ -18829,8 +19111,8 @@
       </c>
     </row>
     <row r="219" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A219" s="3">
-        <v>1547</v>
+      <c r="A219" s="3" t="s">
+        <v>73</v>
       </c>
       <c r="B219" s="4">
         <v>-52.887999999999998</v>
@@ -18873,8 +19155,8 @@
       </c>
     </row>
     <row r="220" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A220" s="3">
-        <v>1547</v>
+      <c r="A220" s="3" t="s">
+        <v>73</v>
       </c>
       <c r="B220" s="4">
         <v>-52.887999999999998</v>
@@ -18917,8 +19199,8 @@
       </c>
     </row>
     <row r="221" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A221" s="3">
-        <v>1547</v>
+      <c r="A221" s="3" t="s">
+        <v>73</v>
       </c>
       <c r="B221" s="4">
         <v>-52.887999999999998</v>
@@ -18961,8 +19243,8 @@
       </c>
     </row>
     <row r="222" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A222" s="3">
-        <v>1547</v>
+      <c r="A222" s="3" t="s">
+        <v>73</v>
       </c>
       <c r="B222" s="4">
         <v>-52.887999999999998</v>
@@ -19005,8 +19287,8 @@
       </c>
     </row>
     <row r="223" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A223" s="3">
-        <v>1748</v>
+      <c r="A223" s="3" t="s">
+        <v>77</v>
       </c>
       <c r="B223" s="4">
         <v>-35.5246</v>
@@ -19049,8 +19331,8 @@
       </c>
     </row>
     <row r="224" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A224" s="3">
-        <v>1748</v>
+      <c r="A224" s="3" t="s">
+        <v>77</v>
       </c>
       <c r="B224" s="4">
         <v>-35.5246</v>
@@ -19093,8 +19375,8 @@
       </c>
     </row>
     <row r="225" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A225" s="3">
-        <v>1748</v>
+      <c r="A225" s="3" t="s">
+        <v>77</v>
       </c>
       <c r="B225" s="4">
         <v>-35.5246</v>
@@ -19137,8 +19419,8 @@
       </c>
     </row>
     <row r="226" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A226" s="3">
-        <v>1748</v>
+      <c r="A226" s="3" t="s">
+        <v>77</v>
       </c>
       <c r="B226" s="4">
         <v>-35.5246</v>
@@ -19181,8 +19463,8 @@
       </c>
     </row>
     <row r="227" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A227" s="3">
-        <v>1748</v>
+      <c r="A227" s="3" t="s">
+        <v>77</v>
       </c>
       <c r="B227" s="4">
         <v>-35.5246</v>
@@ -19225,8 +19507,8 @@
       </c>
     </row>
     <row r="228" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A228" s="3">
-        <v>1748</v>
+      <c r="A228" s="3" t="s">
+        <v>77</v>
       </c>
       <c r="B228" s="4">
         <v>-35.5246</v>
@@ -19269,8 +19551,8 @@
       </c>
     </row>
     <row r="229" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A229" s="3">
-        <v>1748</v>
+      <c r="A229" s="3" t="s">
+        <v>77</v>
       </c>
       <c r="B229" s="4">
         <v>-35.5246</v>
@@ -19313,8 +19595,8 @@
       </c>
     </row>
     <row r="230" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A230" s="3">
-        <v>1788</v>
+      <c r="A230" s="5" t="s">
+        <v>117</v>
       </c>
       <c r="B230" s="4">
         <v>-7.7831999999999999</v>
@@ -19357,8 +19639,8 @@
       </c>
     </row>
     <row r="231" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A231" s="3">
-        <v>1788</v>
+      <c r="A231" s="5" t="s">
+        <v>117</v>
       </c>
       <c r="B231" s="4">
         <v>-7.7831999999999999</v>
@@ -19401,8 +19683,8 @@
       </c>
     </row>
     <row r="232" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A232" s="3">
-        <v>1788</v>
+      <c r="A232" s="5" t="s">
+        <v>117</v>
       </c>
       <c r="B232" s="4">
         <v>-7.7831999999999999</v>
@@ -19445,8 +19727,8 @@
       </c>
     </row>
     <row r="233" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A233" s="3">
-        <v>1788</v>
+      <c r="A233" s="5" t="s">
+        <v>117</v>
       </c>
       <c r="B233" s="4">
         <v>-7.7831999999999999</v>
@@ -19489,8 +19771,8 @@
       </c>
     </row>
     <row r="234" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A234" s="3">
-        <v>1788</v>
+      <c r="A234" s="5" t="s">
+        <v>117</v>
       </c>
       <c r="B234" s="4">
         <v>-7.7831999999999999</v>
@@ -19533,8 +19815,8 @@
       </c>
     </row>
     <row r="235" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A235" s="3">
-        <v>1788</v>
+      <c r="A235" s="5" t="s">
+        <v>117</v>
       </c>
       <c r="B235" s="4">
         <v>-7.7831999999999999</v>
@@ -19577,8 +19859,8 @@
       </c>
     </row>
     <row r="236" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A236" s="3">
-        <v>2158</v>
+      <c r="A236" s="5" t="s">
+        <v>92</v>
       </c>
       <c r="B236" s="4">
         <v>-27.2227</v>
@@ -19621,8 +19903,8 @@
       </c>
     </row>
     <row r="237" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A237" s="3">
-        <v>2158</v>
+      <c r="A237" s="5" t="s">
+        <v>92</v>
       </c>
       <c r="B237" s="4">
         <v>-27.2227</v>
@@ -19665,8 +19947,8 @@
       </c>
     </row>
     <row r="238" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A238" s="3">
-        <v>2158</v>
+      <c r="A238" s="5" t="s">
+        <v>92</v>
       </c>
       <c r="B238" s="4">
         <v>-27.2227</v>
@@ -19709,8 +19991,8 @@
       </c>
     </row>
     <row r="239" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A239" s="3">
-        <v>2158</v>
+      <c r="A239" s="5" t="s">
+        <v>92</v>
       </c>
       <c r="B239" s="4">
         <v>-27.2227</v>
@@ -19753,8 +20035,8 @@
       </c>
     </row>
     <row r="240" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A240" s="3">
-        <v>2158</v>
+      <c r="A240" s="5" t="s">
+        <v>92</v>
       </c>
       <c r="B240" s="4">
         <v>-27.2227</v>
@@ -19797,8 +20079,8 @@
       </c>
     </row>
     <row r="241" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A241" s="3">
-        <v>2158</v>
+      <c r="A241" s="5" t="s">
+        <v>92</v>
       </c>
       <c r="B241" s="4">
         <v>-27.2227</v>
@@ -19841,8 +20123,8 @@
       </c>
     </row>
     <row r="242" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A242" s="3">
-        <v>2158</v>
+      <c r="A242" s="5" t="s">
+        <v>92</v>
       </c>
       <c r="B242" s="4">
         <v>-27.2227</v>
@@ -19885,8 +20167,8 @@
       </c>
     </row>
     <row r="243" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A243" s="3">
-        <v>2158</v>
+      <c r="A243" s="5" t="s">
+        <v>92</v>
       </c>
       <c r="B243" s="4">
         <v>-27.2227</v>
@@ -19929,8 +20211,8 @@
       </c>
     </row>
     <row r="244" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A244" s="3">
-        <v>2158</v>
+      <c r="A244" s="5" t="s">
+        <v>92</v>
       </c>
       <c r="B244" s="4">
         <v>-27.2227</v>
@@ -19973,8 +20255,8 @@
       </c>
     </row>
     <row r="245" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A245" s="3">
-        <v>2158</v>
+      <c r="A245" s="5" t="s">
+        <v>92</v>
       </c>
       <c r="B245" s="4">
         <v>-27.2227</v>
@@ -20017,8 +20299,8 @@
       </c>
     </row>
     <row r="246" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A246" s="3">
-        <v>2158</v>
+      <c r="A246" s="5" t="s">
+        <v>92</v>
       </c>
       <c r="B246" s="4">
         <v>-27.2227</v>
@@ -20061,8 +20343,8 @@
       </c>
     </row>
     <row r="247" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A247" s="3">
-        <v>2158</v>
+      <c r="A247" s="5" t="s">
+        <v>92</v>
       </c>
       <c r="B247" s="4">
         <v>-27.2227</v>
@@ -20105,8 +20387,8 @@
       </c>
     </row>
     <row r="248" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A248" s="3">
-        <v>2158</v>
+      <c r="A248" s="5" t="s">
+        <v>92</v>
       </c>
       <c r="B248" s="4">
         <v>-27.2227</v>
@@ -20149,8 +20431,8 @@
       </c>
     </row>
     <row r="249" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A249" s="3">
-        <v>2158</v>
+      <c r="A249" s="5" t="s">
+        <v>92</v>
       </c>
       <c r="B249" s="4">
         <v>-27.2227</v>
@@ -20193,8 +20475,8 @@
       </c>
     </row>
     <row r="250" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A250" s="3">
-        <v>2158</v>
+      <c r="A250" s="5" t="s">
+        <v>92</v>
       </c>
       <c r="B250" s="4">
         <v>-27.2227</v>
@@ -20237,8 +20519,8 @@
       </c>
     </row>
     <row r="251" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A251" s="3">
-        <v>2158</v>
+      <c r="A251" s="5" t="s">
+        <v>92</v>
       </c>
       <c r="B251" s="4">
         <v>-27.2227</v>
@@ -20281,8 +20563,8 @@
       </c>
     </row>
     <row r="252" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A252" s="3">
-        <v>2158</v>
+      <c r="A252" s="5" t="s">
+        <v>92</v>
       </c>
       <c r="B252" s="4">
         <v>-27.2227</v>
@@ -20325,8 +20607,8 @@
       </c>
     </row>
     <row r="253" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A253" s="3">
-        <v>2158</v>
+      <c r="A253" s="5" t="s">
+        <v>92</v>
       </c>
       <c r="B253" s="4">
         <v>-27.2227</v>
@@ -20369,8 +20651,8 @@
       </c>
     </row>
     <row r="254" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A254" s="3">
-        <v>2158</v>
+      <c r="A254" s="5" t="s">
+        <v>92</v>
       </c>
       <c r="B254" s="4">
         <v>-27.2227</v>
@@ -20413,8 +20695,8 @@
       </c>
     </row>
     <row r="255" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A255" s="3">
-        <v>2158</v>
+      <c r="A255" s="5" t="s">
+        <v>92</v>
       </c>
       <c r="B255" s="4">
         <v>-27.2227</v>
@@ -20457,8 +20739,8 @@
       </c>
     </row>
     <row r="256" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A256" s="3">
-        <v>1916</v>
+      <c r="A256" s="5" t="s">
+        <v>88</v>
       </c>
       <c r="B256" s="4">
         <v>-12.5822</v>
@@ -20501,8 +20783,8 @@
       </c>
     </row>
     <row r="257" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A257" s="3">
-        <v>1916</v>
+      <c r="A257" s="5" t="s">
+        <v>88</v>
       </c>
       <c r="B257" s="4">
         <v>-12.5822</v>
@@ -20545,8 +20827,8 @@
       </c>
     </row>
     <row r="258" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A258" s="3">
-        <v>1916</v>
+      <c r="A258" s="5" t="s">
+        <v>88</v>
       </c>
       <c r="B258" s="4">
         <v>-12.5822</v>
@@ -20589,8 +20871,8 @@
       </c>
     </row>
     <row r="259" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A259" s="3">
-        <v>1916</v>
+      <c r="A259" s="5" t="s">
+        <v>88</v>
       </c>
       <c r="B259" s="4">
         <v>-12.5822</v>
@@ -20633,8 +20915,8 @@
       </c>
     </row>
     <row r="260" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A260" s="3">
-        <v>1916</v>
+      <c r="A260" s="5" t="s">
+        <v>88</v>
       </c>
       <c r="B260" s="4">
         <v>-12.5822</v>
@@ -20677,8 +20959,8 @@
       </c>
     </row>
     <row r="261" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A261" s="3">
-        <v>1916</v>
+      <c r="A261" s="5" t="s">
+        <v>88</v>
       </c>
       <c r="B261" s="4">
         <v>-12.5822</v>
@@ -20721,8 +21003,8 @@
       </c>
     </row>
     <row r="262" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A262" s="3">
-        <v>1916</v>
+      <c r="A262" s="5" t="s">
+        <v>88</v>
       </c>
       <c r="B262" s="4">
         <v>-12.5822</v>
@@ -20765,8 +21047,8 @@
       </c>
     </row>
     <row r="263" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A263" s="3">
-        <v>1916</v>
+      <c r="A263" s="5" t="s">
+        <v>88</v>
       </c>
       <c r="B263" s="4">
         <v>-12.5822</v>
@@ -20809,8 +21091,8 @@
       </c>
     </row>
     <row r="264" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A264" s="3">
-        <v>1916</v>
+      <c r="A264" s="5" t="s">
+        <v>88</v>
       </c>
       <c r="B264" s="4">
         <v>-12.5822</v>
@@ -20853,8 +21135,8 @@
       </c>
     </row>
     <row r="265" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A265" s="3">
-        <v>1916</v>
+      <c r="A265" s="5" t="s">
+        <v>88</v>
       </c>
       <c r="B265" s="4">
         <v>-12.5822</v>
@@ -20897,8 +21179,8 @@
       </c>
     </row>
     <row r="266" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A266" s="3">
-        <v>1916</v>
+      <c r="A266" s="5" t="s">
+        <v>88</v>
       </c>
       <c r="B266" s="4">
         <v>-12.5822</v>
@@ -20941,8 +21223,8 @@
       </c>
     </row>
     <row r="267" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A267" s="3">
-        <v>1916</v>
+      <c r="A267" s="5" t="s">
+        <v>88</v>
       </c>
       <c r="B267" s="4">
         <v>-12.5822</v>
@@ -20985,8 +21267,8 @@
       </c>
     </row>
     <row r="268" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A268" s="3">
-        <v>2389</v>
+      <c r="A268" s="5" t="s">
+        <v>97</v>
       </c>
       <c r="B268" s="4">
         <v>-30.320699999999999</v>
@@ -21029,8 +21311,8 @@
       </c>
     </row>
     <row r="269" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A269" s="3">
-        <v>2389</v>
+      <c r="A269" s="5" t="s">
+        <v>97</v>
       </c>
       <c r="B269" s="4">
         <v>-30.320699999999999</v>
@@ -21073,8 +21355,8 @@
       </c>
     </row>
     <row r="270" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A270" s="3">
-        <v>2389</v>
+      <c r="A270" s="5" t="s">
+        <v>97</v>
       </c>
       <c r="B270" s="4">
         <v>-30.320699999999999</v>
@@ -21117,8 +21399,8 @@
       </c>
     </row>
     <row r="271" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A271" s="3">
-        <v>2389</v>
+      <c r="A271" s="5" t="s">
+        <v>97</v>
       </c>
       <c r="B271" s="4">
         <v>-30.320699999999999</v>
@@ -21161,8 +21443,8 @@
       </c>
     </row>
     <row r="272" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A272" s="3">
-        <v>2389</v>
+      <c r="A272" s="5" t="s">
+        <v>97</v>
       </c>
       <c r="B272" s="4">
         <v>-30.320699999999999</v>
@@ -21205,8 +21487,8 @@
       </c>
     </row>
     <row r="273" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A273" s="3">
-        <v>2389</v>
+      <c r="A273" s="5" t="s">
+        <v>97</v>
       </c>
       <c r="B273" s="4">
         <v>-30.320699999999999</v>
@@ -21249,8 +21531,8 @@
       </c>
     </row>
     <row r="274" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A274" s="3">
-        <v>2389</v>
+      <c r="A274" s="5" t="s">
+        <v>97</v>
       </c>
       <c r="B274" s="4">
         <v>-30.320699999999999</v>
@@ -21293,8 +21575,8 @@
       </c>
     </row>
     <row r="275" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A275" s="3">
-        <v>2389</v>
+      <c r="A275" s="5" t="s">
+        <v>97</v>
       </c>
       <c r="B275" s="4">
         <v>-30.320699999999999</v>
@@ -21337,8 +21619,8 @@
       </c>
     </row>
     <row r="276" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A276" s="3">
-        <v>2389</v>
+      <c r="A276" s="5" t="s">
+        <v>97</v>
       </c>
       <c r="B276" s="4">
         <v>-30.320699999999999</v>
@@ -21381,8 +21663,8 @@
       </c>
     </row>
     <row r="277" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A277" s="3">
-        <v>2389</v>
+      <c r="A277" s="5" t="s">
+        <v>97</v>
       </c>
       <c r="B277" s="4">
         <v>-30.320699999999999</v>
@@ -21425,8 +21707,8 @@
       </c>
     </row>
     <row r="278" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A278" s="3">
-        <v>2389</v>
+      <c r="A278" s="5" t="s">
+        <v>97</v>
       </c>
       <c r="B278" s="4">
         <v>-30.320699999999999</v>
@@ -21469,8 +21751,8 @@
       </c>
     </row>
     <row r="279" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A279" s="3">
-        <v>2389</v>
+      <c r="A279" s="5" t="s">
+        <v>97</v>
       </c>
       <c r="B279" s="4">
         <v>-30.320699999999999</v>
@@ -21513,8 +21795,8 @@
       </c>
     </row>
     <row r="280" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A280" s="3">
-        <v>2389</v>
+      <c r="A280" s="5" t="s">
+        <v>97</v>
       </c>
       <c r="B280" s="4">
         <v>-30.320699999999999</v>
@@ -21557,8 +21839,8 @@
       </c>
     </row>
     <row r="281" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A281" s="3">
-        <v>2389</v>
+      <c r="A281" s="5" t="s">
+        <v>97</v>
       </c>
       <c r="B281" s="4">
         <v>-30.320699999999999</v>
@@ -21601,8 +21883,8 @@
       </c>
     </row>
     <row r="282" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A282" s="3">
-        <v>2389</v>
+      <c r="A282" s="5" t="s">
+        <v>97</v>
       </c>
       <c r="B282" s="4">
         <v>-30.320699999999999</v>
@@ -21645,8 +21927,8 @@
       </c>
     </row>
     <row r="283" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A283" s="3">
-        <v>2389</v>
+      <c r="A283" s="5" t="s">
+        <v>97</v>
       </c>
       <c r="B283" s="4">
         <v>-30.320699999999999</v>
@@ -21689,8 +21971,8 @@
       </c>
     </row>
     <row r="284" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A284" s="3">
-        <v>3341</v>
+      <c r="A284" s="5" t="s">
+        <v>104</v>
       </c>
       <c r="B284" s="4">
         <v>-14.7155</v>
@@ -21733,8 +22015,8 @@
       </c>
     </row>
     <row r="285" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A285" s="3">
-        <v>3341</v>
+      <c r="A285" s="5" t="s">
+        <v>104</v>
       </c>
       <c r="B285" s="4">
         <v>-14.7155</v>
@@ -21777,8 +22059,8 @@
       </c>
     </row>
     <row r="286" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A286" s="3">
-        <v>3341</v>
+      <c r="A286" s="5" t="s">
+        <v>104</v>
       </c>
       <c r="B286" s="4">
         <v>-14.7155</v>
@@ -21821,8 +22103,8 @@
       </c>
     </row>
     <row r="287" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A287" s="3">
-        <v>3341</v>
+      <c r="A287" s="5" t="s">
+        <v>104</v>
       </c>
       <c r="B287" s="4">
         <v>-14.7155</v>
@@ -21865,8 +22147,8 @@
       </c>
     </row>
     <row r="288" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A288" s="3">
-        <v>3341</v>
+      <c r="A288" s="5" t="s">
+        <v>104</v>
       </c>
       <c r="B288" s="4">
         <v>-14.7155</v>
@@ -21909,8 +22191,8 @@
       </c>
     </row>
     <row r="289" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A289" s="3">
-        <v>3341</v>
+      <c r="A289" s="5" t="s">
+        <v>104</v>
       </c>
       <c r="B289" s="4">
         <v>-14.7155</v>
@@ -21953,8 +22235,8 @@
       </c>
     </row>
     <row r="290" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A290" s="3">
-        <v>3341</v>
+      <c r="A290" s="5" t="s">
+        <v>104</v>
       </c>
       <c r="B290" s="4">
         <v>-14.7155</v>
@@ -21997,8 +22279,8 @@
       </c>
     </row>
     <row r="291" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A291" s="3">
-        <v>3341</v>
+      <c r="A291" s="5" t="s">
+        <v>104</v>
       </c>
       <c r="B291" s="4">
         <v>-14.7155</v>
@@ -22041,8 +22323,8 @@
       </c>
     </row>
     <row r="292" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A292" s="3">
-        <v>3341</v>
+      <c r="A292" s="5" t="s">
+        <v>104</v>
       </c>
       <c r="B292" s="4">
         <v>-14.7155</v>
@@ -22085,8 +22367,8 @@
       </c>
     </row>
     <row r="293" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A293" s="3">
-        <v>3341</v>
+      <c r="A293" s="5" t="s">
+        <v>104</v>
       </c>
       <c r="B293" s="4">
         <v>-14.7155</v>
@@ -22129,8 +22411,8 @@
       </c>
     </row>
     <row r="294" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A294" s="3">
-        <v>3341</v>
+      <c r="A294" s="5" t="s">
+        <v>104</v>
       </c>
       <c r="B294" s="4">
         <v>-14.7155</v>
@@ -22173,8 +22455,8 @@
       </c>
     </row>
     <row r="295" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A295" s="3">
-        <v>3341</v>
+      <c r="A295" s="5" t="s">
+        <v>104</v>
       </c>
       <c r="B295" s="4">
         <v>-14.7155</v>
@@ -22217,8 +22499,8 @@
       </c>
     </row>
     <row r="296" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A296" s="3">
-        <v>3341</v>
+      <c r="A296" s="5" t="s">
+        <v>104</v>
       </c>
       <c r="B296" s="4">
         <v>-14.7155</v>
@@ -22261,8 +22543,8 @@
       </c>
     </row>
     <row r="297" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A297" s="3">
-        <v>3341</v>
+      <c r="A297" s="5" t="s">
+        <v>104</v>
       </c>
       <c r="B297" s="4">
         <v>-14.7155</v>
@@ -22305,8 +22587,8 @@
       </c>
     </row>
     <row r="298" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A298" s="3">
-        <v>3341</v>
+      <c r="A298" s="5" t="s">
+        <v>104</v>
       </c>
       <c r="B298" s="4">
         <v>-14.7155</v>
@@ -22349,8 +22631,8 @@
       </c>
     </row>
     <row r="299" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A299" s="3">
-        <v>3341</v>
+      <c r="A299" s="5" t="s">
+        <v>104</v>
       </c>
       <c r="B299" s="4">
         <v>-14.7155</v>
@@ -22393,8 +22675,8 @@
       </c>
     </row>
     <row r="300" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A300" s="3">
-        <v>3513</v>
+      <c r="A300" s="5" t="s">
+        <v>107</v>
       </c>
       <c r="B300" s="4">
         <v>5.3952999999999998</v>
@@ -22437,8 +22719,8 @@
       </c>
     </row>
     <row r="301" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A301" s="3">
-        <v>3513</v>
+      <c r="A301" s="5" t="s">
+        <v>107</v>
       </c>
       <c r="B301" s="4">
         <v>5.3952999999999998</v>
@@ -22481,8 +22763,8 @@
       </c>
     </row>
     <row r="302" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A302" s="3">
-        <v>3513</v>
+      <c r="A302" s="5" t="s">
+        <v>107</v>
       </c>
       <c r="B302" s="4">
         <v>5.3952999999999998</v>
@@ -22525,8 +22807,8 @@
       </c>
     </row>
     <row r="303" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A303" s="3">
-        <v>3513</v>
+      <c r="A303" s="5" t="s">
+        <v>107</v>
       </c>
       <c r="B303" s="4">
         <v>5.3952999999999998</v>
@@ -22569,8 +22851,8 @@
       </c>
     </row>
     <row r="304" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A304" s="3">
-        <v>3513</v>
+      <c r="A304" s="5" t="s">
+        <v>107</v>
       </c>
       <c r="B304" s="4">
         <v>5.3952999999999998</v>
@@ -22613,8 +22895,8 @@
       </c>
     </row>
     <row r="305" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A305" s="3">
-        <v>3513</v>
+      <c r="A305" s="5" t="s">
+        <v>107</v>
       </c>
       <c r="B305" s="4">
         <v>5.3952999999999998</v>
@@ -22657,8 +22939,8 @@
       </c>
     </row>
     <row r="306" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A306" s="3">
-        <v>3513</v>
+      <c r="A306" s="5" t="s">
+        <v>107</v>
       </c>
       <c r="B306" s="4">
         <v>5.3952999999999998</v>
@@ -22701,8 +22983,8 @@
       </c>
     </row>
     <row r="307" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A307" s="3">
-        <v>3513</v>
+      <c r="A307" s="5" t="s">
+        <v>107</v>
       </c>
       <c r="B307" s="4">
         <v>5.3952999999999998</v>
@@ -22745,8 +23027,8 @@
       </c>
     </row>
     <row r="308" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A308" s="3">
-        <v>3513</v>
+      <c r="A308" s="5" t="s">
+        <v>107</v>
       </c>
       <c r="B308" s="4">
         <v>5.3952999999999998</v>
@@ -22789,8 +23071,8 @@
       </c>
     </row>
     <row r="309" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A309" s="3">
-        <v>3513</v>
+      <c r="A309" s="5" t="s">
+        <v>107</v>
       </c>
       <c r="B309" s="4">
         <v>5.3952999999999998</v>
@@ -22833,8 +23115,8 @@
       </c>
     </row>
     <row r="310" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A310" s="3">
-        <v>3513</v>
+      <c r="A310" s="5" t="s">
+        <v>107</v>
       </c>
       <c r="B310" s="4">
         <v>5.3952999999999998</v>
@@ -22877,8 +23159,8 @@
       </c>
     </row>
     <row r="311" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A311" s="3">
-        <v>3513</v>
+      <c r="A311" s="5" t="s">
+        <v>107</v>
       </c>
       <c r="B311" s="4">
         <v>5.3952999999999998</v>
@@ -22921,8 +23203,8 @@
       </c>
     </row>
     <row r="312" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A312" s="3">
-        <v>3513</v>
+      <c r="A312" s="5" t="s">
+        <v>107</v>
       </c>
       <c r="B312" s="4">
         <v>5.3952999999999998</v>
@@ -22965,8 +23247,8 @@
       </c>
     </row>
     <row r="313" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A313" s="3">
-        <v>3513</v>
+      <c r="A313" s="5" t="s">
+        <v>107</v>
       </c>
       <c r="B313" s="4">
         <v>5.3952999999999998</v>
@@ -23009,8 +23291,8 @@
       </c>
     </row>
     <row r="314" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A314" s="3">
-        <v>3513</v>
+      <c r="A314" s="5" t="s">
+        <v>107</v>
       </c>
       <c r="B314" s="4">
         <v>5.3952999999999998</v>
@@ -23053,8 +23335,8 @@
       </c>
     </row>
     <row r="315" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A315" s="3">
-        <v>3513</v>
+      <c r="A315" s="5" t="s">
+        <v>107</v>
       </c>
       <c r="B315" s="4">
         <v>5.3952999999999998</v>
@@ -23097,8 +23379,8 @@
       </c>
     </row>
     <row r="316" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A316" s="3">
-        <v>3513</v>
+      <c r="A316" s="5" t="s">
+        <v>107</v>
       </c>
       <c r="B316" s="4">
         <v>5.3952999999999998</v>
@@ -23141,8 +23423,8 @@
       </c>
     </row>
     <row r="317" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A317" s="3">
-        <v>3513</v>
+      <c r="A317" s="5" t="s">
+        <v>107</v>
       </c>
       <c r="B317" s="4">
         <v>5.3952999999999998</v>
@@ -23185,8 +23467,8 @@
       </c>
     </row>
     <row r="318" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A318" s="3">
-        <v>3513</v>
+      <c r="A318" s="5" t="s">
+        <v>107</v>
       </c>
       <c r="B318" s="4">
         <v>5.3952999999999998</v>
@@ -23229,8 +23511,8 @@
       </c>
     </row>
     <row r="319" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A319" s="3">
-        <v>3513</v>
+      <c r="A319" s="5" t="s">
+        <v>107</v>
       </c>
       <c r="B319" s="4">
         <v>5.3952999999999998</v>
@@ -23273,8 +23555,8 @@
       </c>
     </row>
     <row r="320" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A320" s="3">
-        <v>3513</v>
+      <c r="A320" s="5" t="s">
+        <v>107</v>
       </c>
       <c r="B320" s="4">
         <v>5.3952999999999998</v>
@@ -23317,8 +23599,8 @@
       </c>
     </row>
     <row r="321" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A321" s="3">
-        <v>3952</v>
+      <c r="A321" s="5" t="s">
+        <v>109</v>
       </c>
       <c r="B321" s="4">
         <v>-22.2958</v>
@@ -23361,8 +23643,8 @@
       </c>
     </row>
     <row r="322" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A322" s="3">
-        <v>3952</v>
+      <c r="A322" s="5" t="s">
+        <v>109</v>
       </c>
       <c r="B322" s="4">
         <v>-22.2958</v>
@@ -23405,8 +23687,8 @@
       </c>
     </row>
     <row r="323" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A323" s="3">
-        <v>3952</v>
+      <c r="A323" s="5" t="s">
+        <v>109</v>
       </c>
       <c r="B323" s="4">
         <v>-22.2958</v>
@@ -23449,8 +23731,8 @@
       </c>
     </row>
     <row r="324" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A324" s="3">
-        <v>4858</v>
+      <c r="A324" s="5" t="s">
+        <v>115</v>
       </c>
       <c r="B324" s="4">
         <v>-2.1949999999999998</v>
@@ -23493,8 +23775,8 @@
       </c>
     </row>
     <row r="325" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A325" s="3">
-        <v>4858</v>
+      <c r="A325" s="5" t="s">
+        <v>115</v>
       </c>
       <c r="B325" s="4">
         <v>-2.1949999999999998</v>
@@ -23537,8 +23819,8 @@
       </c>
     </row>
     <row r="326" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A326" s="3">
-        <v>4858</v>
+      <c r="A326" s="5" t="s">
+        <v>115</v>
       </c>
       <c r="B326" s="4">
         <v>-2.1949999999999998</v>
@@ -23581,8 +23863,8 @@
       </c>
     </row>
     <row r="327" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A327" s="3">
-        <v>4858</v>
+      <c r="A327" s="5" t="s">
+        <v>115</v>
       </c>
       <c r="B327" s="4">
         <v>-2.1949999999999998</v>
@@ -23625,8 +23907,8 @@
       </c>
     </row>
     <row r="328" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A328" s="3">
-        <v>4858</v>
+      <c r="A328" s="5" t="s">
+        <v>115</v>
       </c>
       <c r="B328" s="4">
         <v>-2.1949999999999998</v>
@@ -23669,8 +23951,8 @@
       </c>
     </row>
     <row r="329" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A329" s="3">
-        <v>4858</v>
+      <c r="A329" s="5" t="s">
+        <v>115</v>
       </c>
       <c r="B329" s="4">
         <v>-2.1949999999999998</v>
@@ -23713,8 +23995,8 @@
       </c>
     </row>
     <row r="330" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A330" s="3">
-        <v>4858</v>
+      <c r="A330" s="5" t="s">
+        <v>115</v>
       </c>
       <c r="B330" s="4">
         <v>-2.1949999999999998</v>
@@ -23757,8 +24039,8 @@
       </c>
     </row>
     <row r="331" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A331" s="3">
-        <v>4858</v>
+      <c r="A331" s="5" t="s">
+        <v>115</v>
       </c>
       <c r="B331" s="4">
         <v>-2.1949999999999998</v>
@@ -23801,8 +24083,8 @@
       </c>
     </row>
     <row r="332" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A332" s="3">
-        <v>4858</v>
+      <c r="A332" s="5" t="s">
+        <v>115</v>
       </c>
       <c r="B332" s="4">
         <v>-2.1949999999999998</v>
@@ -23845,8 +24127,8 @@
       </c>
     </row>
     <row r="333" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A333" s="3">
-        <v>4858</v>
+      <c r="A333" s="5" t="s">
+        <v>115</v>
       </c>
       <c r="B333" s="4">
         <v>-2.1949999999999998</v>
@@ -23889,8 +24171,8 @@
       </c>
     </row>
     <row r="334" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A334" s="3">
-        <v>4858</v>
+      <c r="A334" s="5" t="s">
+        <v>115</v>
       </c>
       <c r="B334" s="4">
         <v>-2.1949999999999998</v>
@@ -23933,8 +24215,8 @@
       </c>
     </row>
     <row r="335" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A335" s="3">
-        <v>4858</v>
+      <c r="A335" s="5" t="s">
+        <v>115</v>
       </c>
       <c r="B335" s="4">
         <v>-2.1949999999999998</v>
@@ -23977,8 +24259,8 @@
       </c>
     </row>
     <row r="336" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A336" s="3">
-        <v>4858</v>
+      <c r="A336" s="5" t="s">
+        <v>115</v>
       </c>
       <c r="B336" s="4">
         <v>-2.1949999999999998</v>
@@ -24021,8 +24303,8 @@
       </c>
     </row>
     <row r="337" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A337" s="3">
-        <v>4858</v>
+      <c r="A337" s="5" t="s">
+        <v>115</v>
       </c>
       <c r="B337" s="4">
         <v>-2.1949999999999998</v>
@@ -24065,8 +24347,8 @@
       </c>
     </row>
     <row r="338" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A338" s="3">
-        <v>4858</v>
+      <c r="A338" s="5" t="s">
+        <v>115</v>
       </c>
       <c r="B338" s="4">
         <v>-2.1949999999999998</v>
@@ -24109,8 +24391,8 @@
       </c>
     </row>
     <row r="339" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A339" s="3">
-        <v>4858</v>
+      <c r="A339" s="5" t="s">
+        <v>115</v>
       </c>
       <c r="B339" s="4">
         <v>-2.1949999999999998</v>
@@ -24153,8 +24435,8 @@
       </c>
     </row>
     <row r="340" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A340" s="3">
-        <v>4858</v>
+      <c r="A340" s="5" t="s">
+        <v>115</v>
       </c>
       <c r="B340" s="4">
         <v>-2.1949999999999998</v>
@@ -24197,8 +24479,8 @@
       </c>
     </row>
     <row r="341" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A341" s="3">
-        <v>4858</v>
+      <c r="A341" s="5" t="s">
+        <v>115</v>
       </c>
       <c r="B341" s="4">
         <v>-2.1949999999999998</v>
@@ -24241,8 +24523,8 @@
       </c>
     </row>
     <row r="342" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A342" s="3">
-        <v>4858</v>
+      <c r="A342" s="5" t="s">
+        <v>115</v>
       </c>
       <c r="B342" s="4">
         <v>-2.1949999999999998</v>
@@ -24285,8 +24567,8 @@
       </c>
     </row>
     <row r="343" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A343" s="3">
-        <v>4858</v>
+      <c r="A343" s="5" t="s">
+        <v>115</v>
       </c>
       <c r="B343" s="4">
         <v>-2.1949999999999998</v>
@@ -24329,8 +24611,8 @@
       </c>
     </row>
     <row r="344" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A344" s="3">
-        <v>4858</v>
+      <c r="A344" s="5" t="s">
+        <v>115</v>
       </c>
       <c r="B344" s="4">
         <v>-2.1949999999999998</v>
@@ -24373,8 +24655,8 @@
       </c>
     </row>
     <row r="345" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A345" s="3">
-        <v>4858</v>
+      <c r="A345" s="5" t="s">
+        <v>115</v>
       </c>
       <c r="B345" s="4">
         <v>-2.1949999999999998</v>
@@ -24417,8 +24699,8 @@
       </c>
     </row>
     <row r="346" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A346" s="3">
-        <v>4858</v>
+      <c r="A346" s="5" t="s">
+        <v>115</v>
       </c>
       <c r="B346" s="4">
         <v>-2.1949999999999998</v>
@@ -24461,8 +24743,8 @@
       </c>
     </row>
     <row r="347" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A347" s="3">
-        <v>4858</v>
+      <c r="A347" s="5" t="s">
+        <v>115</v>
       </c>
       <c r="B347" s="4">
         <v>-2.1949999999999998</v>
@@ -24505,8 +24787,8 @@
       </c>
     </row>
     <row r="348" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A348" s="3">
-        <v>4858</v>
+      <c r="A348" s="5" t="s">
+        <v>115</v>
       </c>
       <c r="B348" s="4">
         <v>-2.1949999999999998</v>
@@ -24549,8 +24831,8 @@
       </c>
     </row>
     <row r="349" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A349" s="3">
-        <v>4858</v>
+      <c r="A349" s="5" t="s">
+        <v>115</v>
       </c>
       <c r="B349" s="4">
         <v>-2.1949999999999998</v>
@@ -24593,8 +24875,8 @@
       </c>
     </row>
     <row r="350" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A350" s="3">
-        <v>4858</v>
+      <c r="A350" s="5" t="s">
+        <v>115</v>
       </c>
       <c r="B350" s="4">
         <v>-2.1949999999999998</v>
@@ -24637,8 +24919,8 @@
       </c>
     </row>
     <row r="351" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A351" s="3">
-        <v>489</v>
+      <c r="A351" s="3" t="s">
+        <v>64</v>
       </c>
       <c r="B351" s="4">
         <v>-6.577</v>
@@ -24681,8 +24963,8 @@
       </c>
     </row>
     <row r="352" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A352" s="3">
-        <v>489</v>
+      <c r="A352" s="3" t="s">
+        <v>64</v>
       </c>
       <c r="B352" s="4">
         <v>-6.577</v>
@@ -24725,8 +25007,8 @@
       </c>
     </row>
     <row r="353" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A353" s="3">
-        <v>489</v>
+      <c r="A353" s="3" t="s">
+        <v>64</v>
       </c>
       <c r="B353" s="4">
         <v>-6.577</v>
@@ -24769,8 +25051,8 @@
       </c>
     </row>
     <row r="354" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A354" s="3">
-        <v>489</v>
+      <c r="A354" s="3" t="s">
+        <v>64</v>
       </c>
       <c r="B354" s="4">
         <v>-6.577</v>
@@ -24813,8 +25095,8 @@
       </c>
     </row>
     <row r="355" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A355" s="3">
-        <v>2213</v>
+      <c r="A355" s="5" t="s">
+        <v>95</v>
       </c>
       <c r="B355" s="4">
         <v>-6.0052000000000003</v>
@@ -24857,8 +25139,8 @@
       </c>
     </row>
     <row r="356" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A356" s="3">
-        <v>2213</v>
+      <c r="A356" s="5" t="s">
+        <v>95</v>
       </c>
       <c r="B356" s="4">
         <v>-6.0052000000000003</v>
@@ -24901,8 +25183,8 @@
       </c>
     </row>
     <row r="357" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A357" s="3">
-        <v>2213</v>
+      <c r="A357" s="5" t="s">
+        <v>95</v>
       </c>
       <c r="B357" s="4">
         <v>-6.0052000000000003</v>
@@ -24945,8 +25227,8 @@
       </c>
     </row>
     <row r="358" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A358" s="3">
-        <v>2213</v>
+      <c r="A358" s="5" t="s">
+        <v>95</v>
       </c>
       <c r="B358" s="4">
         <v>-6.0052000000000003</v>
@@ -24989,8 +25271,8 @@
       </c>
     </row>
     <row r="359" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A359" s="3">
-        <v>2213</v>
+      <c r="A359" s="5" t="s">
+        <v>95</v>
       </c>
       <c r="B359" s="4">
         <v>-6.0052000000000003</v>
@@ -25033,8 +25315,8 @@
       </c>
     </row>
     <row r="360" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A360" s="3">
-        <v>2527</v>
+      <c r="A360" s="5" t="s">
+        <v>98</v>
       </c>
       <c r="B360" s="4">
         <v>-3.6149</v>
@@ -25077,8 +25359,8 @@
       </c>
     </row>
     <row r="361" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A361" s="3">
-        <v>2527</v>
+      <c r="A361" s="5" t="s">
+        <v>98</v>
       </c>
       <c r="B361" s="4">
         <v>-3.6149</v>
@@ -25121,8 +25403,8 @@
       </c>
     </row>
     <row r="362" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A362" s="3">
-        <v>2527</v>
+      <c r="A362" s="5" t="s">
+        <v>98</v>
       </c>
       <c r="B362" s="4">
         <v>-3.6149</v>
@@ -25165,8 +25447,8 @@
       </c>
     </row>
     <row r="363" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A363" s="3">
-        <v>2527</v>
+      <c r="A363" s="5" t="s">
+        <v>98</v>
       </c>
       <c r="B363" s="4">
         <v>-3.6149</v>
@@ -25209,8 +25491,8 @@
       </c>
     </row>
     <row r="364" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A364" s="3">
-        <v>2527</v>
+      <c r="A364" s="5" t="s">
+        <v>98</v>
       </c>
       <c r="B364" s="4">
         <v>-3.6149</v>
@@ -25253,8 +25535,8 @@
       </c>
     </row>
     <row r="365" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A365" s="3">
-        <v>2527</v>
+      <c r="A365" s="5" t="s">
+        <v>98</v>
       </c>
       <c r="B365" s="4">
         <v>-3.6149</v>
@@ -25297,8 +25579,8 @@
       </c>
     </row>
     <row r="366" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A366" s="3">
-        <v>2527</v>
+      <c r="A366" s="5" t="s">
+        <v>98</v>
       </c>
       <c r="B366" s="4">
         <v>-3.6149</v>
@@ -25341,8 +25623,8 @@
       </c>
     </row>
     <row r="367" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A367" s="3">
-        <v>2527</v>
+      <c r="A367" s="5" t="s">
+        <v>98</v>
       </c>
       <c r="B367" s="4">
         <v>-3.6149</v>
@@ -25385,8 +25667,8 @@
       </c>
     </row>
     <row r="368" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A368" s="3">
-        <v>2733</v>
+      <c r="A368" s="5" t="s">
+        <v>99</v>
       </c>
       <c r="B368" s="4">
         <v>-10.4186</v>
@@ -25429,8 +25711,8 @@
       </c>
     </row>
     <row r="369" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A369" s="3">
-        <v>2733</v>
+      <c r="A369" s="5" t="s">
+        <v>99</v>
       </c>
       <c r="B369" s="4">
         <v>-10.4186</v>
@@ -25473,8 +25755,8 @@
       </c>
     </row>
     <row r="370" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A370" s="3">
-        <v>2733</v>
+      <c r="A370" s="5" t="s">
+        <v>99</v>
       </c>
       <c r="B370" s="4">
         <v>-10.4186</v>
@@ -25517,8 +25799,8 @@
       </c>
     </row>
     <row r="371" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A371" s="3">
-        <v>2733</v>
+      <c r="A371" s="5" t="s">
+        <v>99</v>
       </c>
       <c r="B371" s="4">
         <v>-10.4186</v>
@@ -25561,8 +25843,8 @@
       </c>
     </row>
     <row r="372" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A372" s="3">
-        <v>2733</v>
+      <c r="A372" s="5" t="s">
+        <v>99</v>
       </c>
       <c r="B372" s="4">
         <v>-10.4186</v>
@@ -25605,8 +25887,8 @@
       </c>
     </row>
     <row r="373" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A373" s="3">
-        <v>2733</v>
+      <c r="A373" s="5" t="s">
+        <v>99</v>
       </c>
       <c r="B373" s="4">
         <v>-10.4186</v>
@@ -25649,8 +25931,8 @@
       </c>
     </row>
     <row r="374" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A374" s="3">
-        <v>2733</v>
+      <c r="A374" s="5" t="s">
+        <v>99</v>
       </c>
       <c r="B374" s="4">
         <v>-10.4186</v>
@@ -25693,8 +25975,8 @@
       </c>
     </row>
     <row r="375" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A375" s="3">
-        <v>2733</v>
+      <c r="A375" s="5" t="s">
+        <v>99</v>
       </c>
       <c r="B375" s="4">
         <v>-10.4186</v>
@@ -25737,8 +26019,8 @@
       </c>
     </row>
     <row r="376" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A376" s="3">
-        <v>4262</v>
+      <c r="A376" s="5" t="s">
+        <v>111</v>
       </c>
       <c r="B376" s="4">
         <v>-8.9945000000000004</v>
@@ -25781,8 +26063,8 @@
       </c>
     </row>
     <row r="377" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A377" s="3">
-        <v>4262</v>
+      <c r="A377" s="5" t="s">
+        <v>111</v>
       </c>
       <c r="B377" s="4">
         <v>-8.9945000000000004</v>
@@ -25825,8 +26107,8 @@
       </c>
     </row>
     <row r="378" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A378" s="3">
-        <v>4262</v>
+      <c r="A378" s="5" t="s">
+        <v>111</v>
       </c>
       <c r="B378" s="4">
         <v>-8.9945000000000004</v>
@@ -25869,8 +26151,8 @@
       </c>
     </row>
     <row r="379" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A379" s="3">
-        <v>4262</v>
+      <c r="A379" s="5" t="s">
+        <v>111</v>
       </c>
       <c r="B379" s="4">
         <v>-8.9945000000000004</v>
@@ -25913,8 +26195,8 @@
       </c>
     </row>
     <row r="380" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A380" s="3">
-        <v>4262</v>
+      <c r="A380" s="5" t="s">
+        <v>111</v>
       </c>
       <c r="B380" s="4">
         <v>-8.9945000000000004</v>
@@ -25957,8 +26239,8 @@
       </c>
     </row>
     <row r="381" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A381" s="3">
-        <v>4262</v>
+      <c r="A381" s="5" t="s">
+        <v>111</v>
       </c>
       <c r="B381" s="4">
         <v>-8.9945000000000004</v>
@@ -26001,8 +26283,8 @@
       </c>
     </row>
     <row r="382" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A382" s="3">
-        <v>4262</v>
+      <c r="A382" s="5" t="s">
+        <v>111</v>
       </c>
       <c r="B382" s="4">
         <v>-8.9945000000000004</v>
@@ -26045,8 +26327,8 @@
       </c>
     </row>
     <row r="383" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A383" s="3">
-        <v>3155</v>
+      <c r="A383" s="3" t="s">
+        <v>76</v>
       </c>
       <c r="B383" s="4">
         <v>-11.985799999999999</v>
@@ -26089,8 +26371,8 @@
       </c>
     </row>
     <row r="384" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A384" s="3">
-        <v>3155</v>
+      <c r="A384" s="3" t="s">
+        <v>76</v>
       </c>
       <c r="B384" s="4">
         <v>-11.985799999999999</v>
@@ -26133,8 +26415,8 @@
       </c>
     </row>
     <row r="385" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A385" s="3">
-        <v>3155</v>
+      <c r="A385" s="3" t="s">
+        <v>76</v>
       </c>
       <c r="B385" s="4">
         <v>-11.985799999999999</v>
@@ -26177,8 +26459,8 @@
       </c>
     </row>
     <row r="386" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A386" s="3">
-        <v>3155</v>
+      <c r="A386" s="3" t="s">
+        <v>76</v>
       </c>
       <c r="B386" s="4">
         <v>-11.985799999999999</v>
@@ -26221,8 +26503,8 @@
       </c>
     </row>
     <row r="387" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A387" s="3">
-        <v>3155</v>
+      <c r="A387" s="3" t="s">
+        <v>76</v>
       </c>
       <c r="B387" s="4">
         <v>-11.985799999999999</v>
@@ -26265,8 +26547,8 @@
       </c>
     </row>
     <row r="388" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A388" s="3">
-        <v>3155</v>
+      <c r="A388" s="3" t="s">
+        <v>76</v>
       </c>
       <c r="B388" s="4">
         <v>-11.985799999999999</v>
@@ -26309,8 +26591,8 @@
       </c>
     </row>
     <row r="389" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A389" s="3">
-        <v>3155</v>
+      <c r="A389" s="3" t="s">
+        <v>76</v>
       </c>
       <c r="B389" s="4">
         <v>-11.985799999999999</v>
@@ -26353,8 +26635,8 @@
       </c>
     </row>
     <row r="390" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A390" s="3">
-        <v>3155</v>
+      <c r="A390" s="3" t="s">
+        <v>76</v>
       </c>
       <c r="B390" s="4">
         <v>-11.985799999999999</v>
@@ -26397,8 +26679,8 @@
       </c>
     </row>
     <row r="391" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A391" s="3">
-        <v>3155</v>
+      <c r="A391" s="3" t="s">
+        <v>76</v>
       </c>
       <c r="B391" s="4">
         <v>-11.985799999999999</v>
@@ -26441,8 +26723,8 @@
       </c>
     </row>
     <row r="392" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A392" s="3">
-        <v>3095</v>
+      <c r="A392" s="5" t="s">
+        <v>101</v>
       </c>
       <c r="B392" s="4">
         <v>-14.6107</v>
@@ -26485,8 +26767,8 @@
       </c>
     </row>
     <row r="393" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A393" s="3">
-        <v>3095</v>
+      <c r="A393" s="5" t="s">
+        <v>101</v>
       </c>
       <c r="B393" s="4">
         <v>-14.6107</v>
@@ -26529,8 +26811,8 @@
       </c>
     </row>
     <row r="394" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A394" s="3">
-        <v>3095</v>
+      <c r="A394" s="5" t="s">
+        <v>101</v>
       </c>
       <c r="B394" s="4">
         <v>-14.6107</v>
@@ -26573,8 +26855,8 @@
       </c>
     </row>
     <row r="395" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A395" s="3">
-        <v>3095</v>
+      <c r="A395" s="5" t="s">
+        <v>101</v>
       </c>
       <c r="B395" s="4">
         <v>-14.6107</v>
@@ -26617,8 +26899,8 @@
       </c>
     </row>
     <row r="396" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A396" s="3">
-        <v>3095</v>
+      <c r="A396" s="5" t="s">
+        <v>101</v>
       </c>
       <c r="B396" s="4">
         <v>-14.6107</v>
@@ -26661,8 +26943,8 @@
       </c>
     </row>
     <row r="397" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A397" s="3">
-        <v>3095</v>
+      <c r="A397" s="5" t="s">
+        <v>101</v>
       </c>
       <c r="B397" s="4">
         <v>-14.6107</v>
@@ -26705,8 +26987,8 @@
       </c>
     </row>
     <row r="398" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A398" s="3">
-        <v>303</v>
+      <c r="A398" s="3" t="s">
+        <v>80</v>
       </c>
       <c r="B398" s="4">
         <v>-19.8797</v>
@@ -26749,8 +27031,8 @@
       </c>
     </row>
     <row r="399" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A399" s="3">
-        <v>303</v>
+      <c r="A399" s="3" t="s">
+        <v>80</v>
       </c>
       <c r="B399" s="4">
         <v>-19.8797</v>
@@ -26793,8 +27075,8 @@
       </c>
     </row>
     <row r="400" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A400" s="3">
-        <v>303</v>
+      <c r="A400" s="3" t="s">
+        <v>80</v>
       </c>
       <c r="B400" s="4">
         <v>-19.8797</v>
@@ -26837,8 +27119,8 @@
       </c>
     </row>
     <row r="401" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A401" s="3">
-        <v>303</v>
+      <c r="A401" s="3" t="s">
+        <v>80</v>
       </c>
       <c r="B401" s="4">
         <v>-19.8797</v>
@@ -26881,8 +27163,8 @@
       </c>
     </row>
     <row r="402" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A402" s="3">
-        <v>303</v>
+      <c r="A402" s="3" t="s">
+        <v>80</v>
       </c>
       <c r="B402" s="4">
         <v>-19.8797</v>
@@ -26925,8 +27207,8 @@
       </c>
     </row>
     <row r="403" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A403" s="3">
-        <v>303</v>
+      <c r="A403" s="3" t="s">
+        <v>80</v>
       </c>
       <c r="B403" s="4">
         <v>-19.8797</v>
@@ -26969,8 +27251,8 @@
       </c>
     </row>
     <row r="404" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A404" s="3">
-        <v>303</v>
+      <c r="A404" s="3" t="s">
+        <v>80</v>
       </c>
       <c r="B404" s="4">
         <v>-19.8797</v>
@@ -27013,8 +27295,8 @@
       </c>
     </row>
     <row r="405" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A405" s="3">
-        <v>303</v>
+      <c r="A405" s="3" t="s">
+        <v>80</v>
       </c>
       <c r="B405" s="4">
         <v>-19.8797</v>
@@ -27057,8 +27339,8 @@
       </c>
     </row>
     <row r="406" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A406" s="3">
-        <v>303</v>
+      <c r="A406" s="3" t="s">
+        <v>80</v>
       </c>
       <c r="B406" s="4">
         <v>-19.8797</v>
@@ -27101,8 +27383,8 @@
       </c>
     </row>
     <row r="407" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A407" s="3">
-        <v>303</v>
+      <c r="A407" s="3" t="s">
+        <v>80</v>
       </c>
       <c r="B407" s="4">
         <v>-19.8797</v>
@@ -27145,8 +27427,8 @@
       </c>
     </row>
     <row r="408" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A408" s="3">
-        <v>1191</v>
+      <c r="A408" s="3" t="s">
+        <v>68</v>
       </c>
       <c r="B408" s="4">
         <v>-7.0491000000000001</v>
@@ -27189,8 +27471,8 @@
       </c>
     </row>
     <row r="409" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A409" s="3">
-        <v>1191</v>
+      <c r="A409" s="3" t="s">
+        <v>68</v>
       </c>
       <c r="B409" s="4">
         <v>-7.0491000000000001</v>
@@ -27233,8 +27515,8 @@
       </c>
     </row>
     <row r="410" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A410" s="3">
-        <v>1191</v>
+      <c r="A410" s="3" t="s">
+        <v>68</v>
       </c>
       <c r="B410" s="4">
         <v>-7.0491000000000001</v>
@@ -27277,8 +27559,8 @@
       </c>
     </row>
     <row r="411" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A411" s="3">
-        <v>1191</v>
+      <c r="A411" s="3" t="s">
+        <v>68</v>
       </c>
       <c r="B411" s="4">
         <v>-7.0491000000000001</v>
@@ -27321,8 +27603,8 @@
       </c>
     </row>
     <row r="412" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A412" s="3">
-        <v>1191</v>
+      <c r="A412" s="3" t="s">
+        <v>68</v>
       </c>
       <c r="B412" s="4">
         <v>-7.0491000000000001</v>
@@ -27365,8 +27647,8 @@
       </c>
     </row>
     <row r="413" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A413" s="3">
-        <v>1191</v>
+      <c r="A413" s="3" t="s">
+        <v>68</v>
       </c>
       <c r="B413" s="4">
         <v>-7.0491000000000001</v>
@@ -27409,8 +27691,8 @@
       </c>
     </row>
     <row r="414" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A414" s="3">
-        <v>1677</v>
+      <c r="A414" s="3" t="s">
+        <v>75</v>
       </c>
       <c r="B414" s="4">
         <v>-21.529499999999999</v>
@@ -27453,8 +27735,8 @@
       </c>
     </row>
     <row r="415" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A415" s="3">
-        <v>1677</v>
+      <c r="A415" s="3" t="s">
+        <v>75</v>
       </c>
       <c r="B415" s="4">
         <v>-21.529499999999999</v>
@@ -27497,8 +27779,8 @@
       </c>
     </row>
     <row r="416" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A416" s="3">
-        <v>1677</v>
+      <c r="A416" s="3" t="s">
+        <v>75</v>
       </c>
       <c r="B416" s="4">
         <v>-21.529499999999999</v>
@@ -27541,8 +27823,8 @@
       </c>
     </row>
     <row r="417" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A417" s="3">
-        <v>1677</v>
+      <c r="A417" s="3" t="s">
+        <v>75</v>
       </c>
       <c r="B417" s="4">
         <v>-21.529499999999999</v>
@@ -27585,8 +27867,8 @@
       </c>
     </row>
     <row r="418" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A418" s="3">
-        <v>1677</v>
+      <c r="A418" s="3" t="s">
+        <v>75</v>
       </c>
       <c r="B418" s="4">
         <v>-21.529499999999999</v>
@@ -27629,8 +27911,8 @@
       </c>
     </row>
     <row r="419" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A419" s="3">
-        <v>1677</v>
+      <c r="A419" s="3" t="s">
+        <v>75</v>
       </c>
       <c r="B419" s="4">
         <v>-21.529499999999999</v>
@@ -27673,8 +27955,8 @@
       </c>
     </row>
     <row r="420" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A420" s="3">
-        <v>1677</v>
+      <c r="A420" s="3" t="s">
+        <v>75</v>
       </c>
       <c r="B420" s="4">
         <v>-21.529499999999999</v>
@@ -27717,8 +27999,8 @@
       </c>
     </row>
     <row r="421" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A421" s="3">
-        <v>1677</v>
+      <c r="A421" s="3" t="s">
+        <v>75</v>
       </c>
       <c r="B421" s="4">
         <v>-21.529499999999999</v>
@@ -27761,8 +28043,8 @@
       </c>
     </row>
     <row r="422" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A422" s="3">
-        <v>2292</v>
+      <c r="A422" s="5" t="s">
+        <v>96</v>
       </c>
       <c r="B422" s="4">
         <v>-14.2278</v>
@@ -27805,8 +28087,8 @@
       </c>
     </row>
     <row r="423" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A423" s="3">
-        <v>2292</v>
+      <c r="A423" s="5" t="s">
+        <v>96</v>
       </c>
       <c r="B423" s="4">
         <v>-14.2278</v>
@@ -27849,8 +28131,8 @@
       </c>
     </row>
     <row r="424" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A424" s="3">
-        <v>2292</v>
+      <c r="A424" s="5" t="s">
+        <v>96</v>
       </c>
       <c r="B424" s="4">
         <v>-14.2278</v>
@@ -27893,8 +28175,8 @@
       </c>
     </row>
     <row r="425" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A425" s="3">
-        <v>2292</v>
+      <c r="A425" s="5" t="s">
+        <v>96</v>
       </c>
       <c r="B425" s="4">
         <v>-14.2278</v>
@@ -27937,8 +28219,8 @@
       </c>
     </row>
     <row r="426" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A426" s="3">
-        <v>2292</v>
+      <c r="A426" s="5" t="s">
+        <v>96</v>
       </c>
       <c r="B426" s="4">
         <v>-14.2278</v>
@@ -27981,8 +28263,8 @@
       </c>
     </row>
     <row r="427" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A427" s="3">
-        <v>3192</v>
+      <c r="A427" s="5" t="s">
+        <v>103</v>
       </c>
       <c r="B427" s="4">
         <v>-26.321000000000002</v>
@@ -28025,8 +28307,8 @@
       </c>
     </row>
     <row r="428" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A428" s="3">
-        <v>3192</v>
+      <c r="A428" s="5" t="s">
+        <v>103</v>
       </c>
       <c r="B428" s="4">
         <v>-26.321000000000002</v>
@@ -28069,8 +28351,8 @@
       </c>
     </row>
     <row r="429" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A429" s="3">
-        <v>3192</v>
+      <c r="A429" s="5" t="s">
+        <v>103</v>
       </c>
       <c r="B429" s="4">
         <v>-26.321000000000002</v>
@@ -28113,8 +28395,8 @@
       </c>
     </row>
     <row r="430" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A430" s="3">
-        <v>3192</v>
+      <c r="A430" s="5" t="s">
+        <v>103</v>
       </c>
       <c r="B430" s="4">
         <v>-26.321000000000002</v>
@@ -28157,8 +28439,8 @@
       </c>
     </row>
     <row r="431" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A431" s="3">
-        <v>3192</v>
+      <c r="A431" s="5" t="s">
+        <v>103</v>
       </c>
       <c r="B431" s="4">
         <v>-26.321000000000002</v>
@@ -28201,8 +28483,8 @@
       </c>
     </row>
     <row r="432" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A432" s="3">
-        <v>3192</v>
+      <c r="A432" s="5" t="s">
+        <v>103</v>
       </c>
       <c r="B432" s="4">
         <v>-26.321000000000002</v>
@@ -28245,8 +28527,8 @@
       </c>
     </row>
     <row r="433" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A433" s="3">
-        <v>3342</v>
+      <c r="A433" s="5" t="s">
+        <v>105</v>
       </c>
       <c r="B433" s="4">
         <v>-17.876000000000001</v>
@@ -28289,8 +28571,8 @@
       </c>
     </row>
     <row r="434" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A434" s="3">
-        <v>3342</v>
+      <c r="A434" s="5" t="s">
+        <v>105</v>
       </c>
       <c r="B434" s="4">
         <v>-17.876000000000001</v>
@@ -28333,8 +28615,8 @@
       </c>
     </row>
     <row r="435" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A435" s="3">
-        <v>3342</v>
+      <c r="A435" s="5" t="s">
+        <v>105</v>
       </c>
       <c r="B435" s="4">
         <v>-17.876000000000001</v>
@@ -28377,8 +28659,8 @@
       </c>
     </row>
     <row r="436" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A436" s="3">
-        <v>3342</v>
+      <c r="A436" s="5" t="s">
+        <v>105</v>
       </c>
       <c r="B436" s="4">
         <v>-17.876000000000001</v>
@@ -28421,8 +28703,8 @@
       </c>
     </row>
     <row r="437" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A437" s="3">
-        <v>3342</v>
+      <c r="A437" s="5" t="s">
+        <v>105</v>
       </c>
       <c r="B437" s="4">
         <v>-17.876000000000001</v>
@@ -28465,8 +28747,8 @@
       </c>
     </row>
     <row r="438" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A438" s="3">
-        <v>3342</v>
+      <c r="A438" s="5" t="s">
+        <v>105</v>
       </c>
       <c r="B438" s="4">
         <v>-17.876000000000001</v>
@@ -28509,8 +28791,8 @@
       </c>
     </row>
     <row r="439" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A439" s="3">
-        <v>3342</v>
+      <c r="A439" s="5" t="s">
+        <v>105</v>
       </c>
       <c r="B439" s="4">
         <v>-17.876000000000001</v>
@@ -28553,8 +28835,8 @@
       </c>
     </row>
     <row r="440" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A440" s="3">
-        <v>3342</v>
+      <c r="A440" s="5" t="s">
+        <v>105</v>
       </c>
       <c r="B440" s="4">
         <v>-17.876000000000001</v>
@@ -28597,8 +28879,8 @@
       </c>
     </row>
     <row r="441" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A441" s="3">
-        <v>3506</v>
+      <c r="A441" s="5" t="s">
+        <v>106</v>
       </c>
       <c r="B441" s="4">
         <v>-31.688700000000001</v>
@@ -28641,8 +28923,8 @@
       </c>
     </row>
     <row r="442" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A442" s="3">
-        <v>3506</v>
+      <c r="A442" s="5" t="s">
+        <v>106</v>
       </c>
       <c r="B442" s="4">
         <v>-31.688700000000001</v>
@@ -28685,8 +28967,8 @@
       </c>
     </row>
     <row r="443" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A443" s="3">
-        <v>3506</v>
+      <c r="A443" s="5" t="s">
+        <v>106</v>
       </c>
       <c r="B443" s="4">
         <v>-31.688700000000001</v>
@@ -28729,8 +29011,8 @@
       </c>
     </row>
     <row r="444" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A444" s="3">
-        <v>3506</v>
+      <c r="A444" s="5" t="s">
+        <v>106</v>
       </c>
       <c r="B444" s="4">
         <v>-31.688700000000001</v>
@@ -28773,8 +29055,8 @@
       </c>
     </row>
     <row r="445" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A445" s="3">
-        <v>3506</v>
+      <c r="A445" s="5" t="s">
+        <v>106</v>
       </c>
       <c r="B445" s="4">
         <v>-31.688700000000001</v>
@@ -28817,8 +29099,8 @@
       </c>
     </row>
     <row r="446" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A446" s="3">
-        <v>3506</v>
+      <c r="A446" s="5" t="s">
+        <v>106</v>
       </c>
       <c r="B446" s="4">
         <v>-31.688700000000001</v>
@@ -28861,8 +29143,8 @@
       </c>
     </row>
     <row r="447" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A447" s="3">
-        <v>3506</v>
+      <c r="A447" s="5" t="s">
+        <v>106</v>
       </c>
       <c r="B447" s="4">
         <v>-31.688700000000001</v>
@@ -28905,8 +29187,8 @@
       </c>
     </row>
     <row r="448" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A448" s="3">
-        <v>3506</v>
+      <c r="A448" s="5" t="s">
+        <v>106</v>
       </c>
       <c r="B448" s="4">
         <v>-31.688700000000001</v>
@@ -28949,8 +29231,8 @@
       </c>
     </row>
     <row r="449" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A449" s="3">
-        <v>3506</v>
+      <c r="A449" s="5" t="s">
+        <v>106</v>
       </c>
       <c r="B449" s="4">
         <v>-31.688700000000001</v>
@@ -28993,8 +29275,8 @@
       </c>
     </row>
     <row r="450" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A450" s="3">
-        <v>3506</v>
+      <c r="A450" s="5" t="s">
+        <v>106</v>
       </c>
       <c r="B450" s="4">
         <v>-31.688700000000001</v>
@@ -29037,8 +29319,8 @@
       </c>
     </row>
     <row r="451" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A451" s="3">
-        <v>3506</v>
+      <c r="A451" s="5" t="s">
+        <v>106</v>
       </c>
       <c r="B451" s="4">
         <v>-31.688700000000001</v>
@@ -29081,8 +29363,8 @@
       </c>
     </row>
     <row r="452" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A452" s="3">
-        <v>3506</v>
+      <c r="A452" s="5" t="s">
+        <v>106</v>
       </c>
       <c r="B452" s="4">
         <v>-31.688700000000001</v>
@@ -29125,8 +29407,8 @@
       </c>
     </row>
     <row r="453" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A453" s="3">
-        <v>3506</v>
+      <c r="A453" s="5" t="s">
+        <v>106</v>
       </c>
       <c r="B453" s="4">
         <v>-31.688700000000001</v>
@@ -29169,8 +29451,8 @@
       </c>
     </row>
     <row r="454" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A454" s="3">
-        <v>3506</v>
+      <c r="A454" s="5" t="s">
+        <v>106</v>
       </c>
       <c r="B454" s="4">
         <v>-31.688700000000001</v>
@@ -29213,8 +29495,8 @@
       </c>
     </row>
     <row r="455" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A455" s="3">
-        <v>3506</v>
+      <c r="A455" s="5" t="s">
+        <v>106</v>
       </c>
       <c r="B455" s="4">
         <v>-31.688700000000001</v>
@@ -29257,8 +29539,8 @@
       </c>
     </row>
     <row r="456" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A456" s="3">
-        <v>3506</v>
+      <c r="A456" s="5" t="s">
+        <v>106</v>
       </c>
       <c r="B456" s="4">
         <v>-31.688700000000001</v>
@@ -29301,8 +29583,8 @@
       </c>
     </row>
     <row r="457" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A457" s="3">
-        <v>3821</v>
+      <c r="A457" s="5" t="s">
+        <v>108</v>
       </c>
       <c r="B457" s="4">
         <v>-30.901499999999999</v>
@@ -29345,8 +29627,8 @@
       </c>
     </row>
     <row r="458" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A458" s="3">
-        <v>3821</v>
+      <c r="A458" s="5" t="s">
+        <v>108</v>
       </c>
       <c r="B458" s="4">
         <v>-30.901499999999999</v>
@@ -29389,8 +29671,8 @@
       </c>
     </row>
     <row r="459" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A459" s="3">
-        <v>3821</v>
+      <c r="A459" s="5" t="s">
+        <v>108</v>
       </c>
       <c r="B459" s="4">
         <v>-30.901499999999999</v>
@@ -29433,8 +29715,8 @@
       </c>
     </row>
     <row r="460" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A460" s="3">
-        <v>3821</v>
+      <c r="A460" s="5" t="s">
+        <v>108</v>
       </c>
       <c r="B460" s="4">
         <v>-30.901499999999999</v>
@@ -29477,8 +29759,8 @@
       </c>
     </row>
     <row r="461" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A461" s="3">
-        <v>3821</v>
+      <c r="A461" s="5" t="s">
+        <v>108</v>
       </c>
       <c r="B461" s="4">
         <v>-30.901499999999999</v>
@@ -29521,8 +29803,8 @@
       </c>
     </row>
     <row r="462" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A462" s="3">
-        <v>3821</v>
+      <c r="A462" s="5" t="s">
+        <v>108</v>
       </c>
       <c r="B462" s="4">
         <v>-30.901499999999999</v>
@@ -29565,8 +29847,8 @@
       </c>
     </row>
     <row r="463" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A463" s="3">
-        <v>4583</v>
+      <c r="A463" s="5" t="s">
+        <v>116</v>
       </c>
       <c r="B463" s="4">
         <v>-20.225300000000001</v>
@@ -29609,8 +29891,8 @@
       </c>
     </row>
     <row r="464" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A464" s="3">
-        <v>4583</v>
+      <c r="A464" s="5" t="s">
+        <v>116</v>
       </c>
       <c r="B464" s="4">
         <v>-20.225300000000001</v>
@@ -29653,8 +29935,8 @@
       </c>
     </row>
     <row r="465" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A465" s="3">
-        <v>4583</v>
+      <c r="A465" s="5" t="s">
+        <v>116</v>
       </c>
       <c r="B465" s="4">
         <v>-20.225300000000001</v>
@@ -29697,8 +29979,8 @@
       </c>
     </row>
     <row r="466" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A466" s="3">
-        <v>4583</v>
+      <c r="A466" s="5" t="s">
+        <v>116</v>
       </c>
       <c r="B466" s="4">
         <v>-20.225300000000001</v>
@@ -29741,8 +30023,8 @@
       </c>
     </row>
     <row r="467" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A467" s="3">
-        <v>4583</v>
+      <c r="A467" s="5" t="s">
+        <v>116</v>
       </c>
       <c r="B467" s="4">
         <v>-20.225300000000001</v>
@@ -29785,8 +30067,8 @@
       </c>
     </row>
     <row r="468" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A468" s="3">
-        <v>4583</v>
+      <c r="A468" s="5" t="s">
+        <v>116</v>
       </c>
       <c r="B468" s="4">
         <v>-20.225300000000001</v>
@@ -29829,8 +30111,8 @@
       </c>
     </row>
     <row r="469" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A469" s="3">
-        <v>4583</v>
+      <c r="A469" s="5" t="s">
+        <v>116</v>
       </c>
       <c r="B469" s="4">
         <v>-20.225300000000001</v>
@@ -29873,8 +30155,8 @@
       </c>
     </row>
     <row r="470" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A470" s="3">
-        <v>1163</v>
+      <c r="A470" s="3" t="s">
+        <v>67</v>
       </c>
       <c r="B470" s="4">
         <v>-14.1966</v>
@@ -29917,8 +30199,8 @@
       </c>
     </row>
     <row r="471" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A471" s="3">
-        <v>1163</v>
+      <c r="A471" s="3" t="s">
+        <v>67</v>
       </c>
       <c r="B471" s="4">
         <v>-14.1966</v>
@@ -29961,8 +30243,8 @@
       </c>
     </row>
     <row r="472" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A472" s="3">
-        <v>1163</v>
+      <c r="A472" s="3" t="s">
+        <v>67</v>
       </c>
       <c r="B472" s="4">
         <v>-14.1966</v>
@@ -30005,8 +30287,8 @@
       </c>
     </row>
     <row r="473" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A473" s="3">
-        <v>1163</v>
+      <c r="A473" s="3" t="s">
+        <v>67</v>
       </c>
       <c r="B473" s="4">
         <v>-14.1966</v>
@@ -30049,8 +30331,8 @@
       </c>
     </row>
     <row r="474" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A474" s="3">
-        <v>1163</v>
+      <c r="A474" s="3" t="s">
+        <v>67</v>
       </c>
       <c r="B474" s="4">
         <v>-14.1966</v>
@@ -30093,8 +30375,8 @@
       </c>
     </row>
     <row r="475" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A475" s="3">
-        <v>1163</v>
+      <c r="A475" s="3" t="s">
+        <v>67</v>
       </c>
       <c r="B475" s="4">
         <v>-14.1966</v>
@@ -30137,8 +30419,8 @@
       </c>
     </row>
     <row r="476" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A476" s="3">
-        <v>2818</v>
+      <c r="A476" s="5" t="s">
+        <v>100</v>
       </c>
       <c r="B476" s="4">
         <v>-6.7805</v>
@@ -30181,8 +30463,8 @@
       </c>
     </row>
     <row r="477" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A477" s="3">
-        <v>2818</v>
+      <c r="A477" s="5" t="s">
+        <v>100</v>
       </c>
       <c r="B477" s="4">
         <v>-6.7805</v>
@@ -30225,8 +30507,8 @@
       </c>
     </row>
     <row r="478" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A478" s="3">
-        <v>2818</v>
+      <c r="A478" s="5" t="s">
+        <v>100</v>
       </c>
       <c r="B478" s="4">
         <v>-6.7805</v>
@@ -30269,8 +30551,8 @@
       </c>
     </row>
     <row r="479" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A479" s="3">
-        <v>2818</v>
+      <c r="A479" s="5" t="s">
+        <v>100</v>
       </c>
       <c r="B479" s="4">
         <v>-6.7805</v>
@@ -30313,8 +30595,8 @@
       </c>
     </row>
     <row r="480" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A480" s="3">
-        <v>2818</v>
+      <c r="A480" s="5" t="s">
+        <v>100</v>
       </c>
       <c r="B480" s="4">
         <v>-6.7805</v>
@@ -30357,8 +30639,8 @@
       </c>
     </row>
     <row r="481" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A481" s="3">
-        <v>2818</v>
+      <c r="A481" s="5" t="s">
+        <v>100</v>
       </c>
       <c r="B481" s="4">
         <v>-6.7805</v>
@@ -30401,8 +30683,8 @@
       </c>
     </row>
     <row r="482" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A482" s="3">
-        <v>2818</v>
+      <c r="A482" s="5" t="s">
+        <v>100</v>
       </c>
       <c r="B482" s="4">
         <v>-6.7805</v>
@@ -30445,8 +30727,8 @@
       </c>
     </row>
     <row r="483" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A483" s="3">
-        <v>2818</v>
+      <c r="A483" s="5" t="s">
+        <v>100</v>
       </c>
       <c r="B483" s="4">
         <v>-6.7805</v>
@@ -30489,8 +30771,8 @@
       </c>
     </row>
     <row r="484" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A484" s="3">
-        <v>2818</v>
+      <c r="A484" s="5" t="s">
+        <v>100</v>
       </c>
       <c r="B484" s="4">
         <v>-6.7805</v>
@@ -30533,8 +30815,8 @@
       </c>
     </row>
     <row r="485" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A485" s="3">
-        <v>2818</v>
+      <c r="A485" s="5" t="s">
+        <v>100</v>
       </c>
       <c r="B485" s="4">
         <v>-6.7805</v>
@@ -30574,6 +30856,842 @@
       </c>
       <c r="N485" s="4">
         <v>589.91470000000004</v>
+      </c>
+    </row>
+    <row r="486" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A486" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="B486" s="4">
+        <v>-11.985799999999999</v>
+      </c>
+      <c r="C486" s="4">
+        <v>32.903300000000002</v>
+      </c>
+      <c r="D486" s="4">
+        <v>397.05500000000001</v>
+      </c>
+      <c r="E486" s="4">
+        <v>-0.1552</v>
+      </c>
+      <c r="F486" s="4">
+        <v>0.98340000000000005</v>
+      </c>
+      <c r="G486" s="4">
+        <v>9.3700000000000006E-2</v>
+      </c>
+      <c r="H486" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I486" s="4">
+        <v>11.043699999999999</v>
+      </c>
+      <c r="J486" s="4">
+        <v>34.4681</v>
+      </c>
+      <c r="K486" s="4">
+        <v>373.68959999999998</v>
+      </c>
+      <c r="L486" s="4">
+        <v>12.2178</v>
+      </c>
+      <c r="M486" s="4">
+        <v>25.632200000000001</v>
+      </c>
+      <c r="N486" s="4">
+        <v>377.96050000000002</v>
+      </c>
+    </row>
+    <row r="487" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A487" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="B487" s="4">
+        <v>-11.985799999999999</v>
+      </c>
+      <c r="C487" s="4">
+        <v>32.903300000000002</v>
+      </c>
+      <c r="D487" s="4">
+        <v>397.05500000000001</v>
+      </c>
+      <c r="E487" s="4">
+        <v>-0.1552</v>
+      </c>
+      <c r="F487" s="4">
+        <v>0.98340000000000005</v>
+      </c>
+      <c r="G487" s="4">
+        <v>9.3700000000000006E-2</v>
+      </c>
+      <c r="H487" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I487" s="4">
+        <v>7.3651999999999997</v>
+      </c>
+      <c r="J487" s="4">
+        <v>24.101199999999999</v>
+      </c>
+      <c r="K487" s="4">
+        <v>376.37549999999999</v>
+      </c>
+      <c r="L487" s="4">
+        <v>15.230700000000001</v>
+      </c>
+      <c r="M487" s="4">
+        <v>9.7881999999999998</v>
+      </c>
+      <c r="N487" s="4">
+        <v>387.0256</v>
+      </c>
+    </row>
+    <row r="488" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A488" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="B488" s="4">
+        <v>-11.985799999999999</v>
+      </c>
+      <c r="C488" s="4">
+        <v>32.903300000000002</v>
+      </c>
+      <c r="D488" s="4">
+        <v>397.05500000000001</v>
+      </c>
+      <c r="E488" s="4">
+        <v>-0.1552</v>
+      </c>
+      <c r="F488" s="4">
+        <v>0.98340000000000005</v>
+      </c>
+      <c r="G488" s="4">
+        <v>9.3700000000000006E-2</v>
+      </c>
+      <c r="H488" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I488" s="4">
+        <v>-29.493500000000001</v>
+      </c>
+      <c r="J488" s="4">
+        <v>42.877200000000002</v>
+      </c>
+      <c r="K488" s="4">
+        <v>370.62979999999999</v>
+      </c>
+      <c r="L488" s="4">
+        <v>-40.017099999999999</v>
+      </c>
+      <c r="M488" s="4">
+        <v>28.341100000000001</v>
+      </c>
+      <c r="N488" s="4">
+        <v>381.79759999999999</v>
+      </c>
+    </row>
+    <row r="489" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A489" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="B489" s="4">
+        <v>-11.985799999999999</v>
+      </c>
+      <c r="C489" s="4">
+        <v>32.903300000000002</v>
+      </c>
+      <c r="D489" s="4">
+        <v>397.05500000000001</v>
+      </c>
+      <c r="E489" s="4">
+        <v>-0.1552</v>
+      </c>
+      <c r="F489" s="4">
+        <v>0.98340000000000005</v>
+      </c>
+      <c r="G489" s="4">
+        <v>9.3700000000000006E-2</v>
+      </c>
+      <c r="H489" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I489" s="4">
+        <v>-18.649999999999999</v>
+      </c>
+      <c r="J489" s="4">
+        <v>35.701000000000001</v>
+      </c>
+      <c r="K489" s="4">
+        <v>365.41730000000001</v>
+      </c>
+      <c r="L489" s="4">
+        <v>-24.659700000000001</v>
+      </c>
+      <c r="M489" s="4">
+        <v>22.562799999999999</v>
+      </c>
+      <c r="N489" s="4">
+        <v>371.69850000000002</v>
+      </c>
+    </row>
+    <row r="490" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A490" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="B490" s="4">
+        <v>-11.985799999999999</v>
+      </c>
+      <c r="C490" s="4">
+        <v>32.903300000000002</v>
+      </c>
+      <c r="D490" s="4">
+        <v>397.05500000000001</v>
+      </c>
+      <c r="E490" s="4">
+        <v>-0.1552</v>
+      </c>
+      <c r="F490" s="4">
+        <v>0.98340000000000005</v>
+      </c>
+      <c r="G490" s="4">
+        <v>9.3700000000000006E-2</v>
+      </c>
+      <c r="H490" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I490" s="4">
+        <v>-27.752300000000002</v>
+      </c>
+      <c r="J490" s="4">
+        <v>28.7806</v>
+      </c>
+      <c r="K490" s="4">
+        <v>373.32479999999998</v>
+      </c>
+      <c r="L490" s="4">
+        <v>-40.482599999999998</v>
+      </c>
+      <c r="M490" s="4">
+        <v>7.3494999999999999</v>
+      </c>
+      <c r="N490" s="4">
+        <v>397.22800000000001</v>
+      </c>
+    </row>
+    <row r="491" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A491" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="B491" s="4">
+        <v>-11.985799999999999</v>
+      </c>
+      <c r="C491" s="4">
+        <v>32.903300000000002</v>
+      </c>
+      <c r="D491" s="4">
+        <v>397.05500000000001</v>
+      </c>
+      <c r="E491" s="4">
+        <v>-0.1552</v>
+      </c>
+      <c r="F491" s="4">
+        <v>0.98340000000000005</v>
+      </c>
+      <c r="G491" s="4">
+        <v>9.3700000000000006E-2</v>
+      </c>
+      <c r="H491" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I491" s="4">
+        <v>-16.264900000000001</v>
+      </c>
+      <c r="J491" s="4">
+        <v>21.847999999999999</v>
+      </c>
+      <c r="K491" s="4">
+        <v>372.11790000000002</v>
+      </c>
+      <c r="L491" s="4">
+        <v>-15.027100000000001</v>
+      </c>
+      <c r="M491" s="4">
+        <v>-2.9178000000000002</v>
+      </c>
+      <c r="N491" s="4">
+        <v>396.68520000000001</v>
+      </c>
+    </row>
+    <row r="492" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A492" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="B492" s="4">
+        <v>-11.985799999999999</v>
+      </c>
+      <c r="C492" s="4">
+        <v>32.903300000000002</v>
+      </c>
+      <c r="D492" s="4">
+        <v>397.05500000000001</v>
+      </c>
+      <c r="E492" s="4">
+        <v>-0.1552</v>
+      </c>
+      <c r="F492" s="4">
+        <v>0.98340000000000005</v>
+      </c>
+      <c r="G492" s="4">
+        <v>9.3700000000000006E-2</v>
+      </c>
+      <c r="H492" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I492" s="4">
+        <v>-1.5522</v>
+      </c>
+      <c r="J492" s="4">
+        <v>12.078099999999999</v>
+      </c>
+      <c r="K492" s="4">
+        <v>379.59960000000001</v>
+      </c>
+      <c r="L492" s="4">
+        <v>0.9677</v>
+      </c>
+      <c r="M492" s="4">
+        <v>-0.71140000000000003</v>
+      </c>
+      <c r="N492" s="4">
+        <v>396.95920000000001</v>
+      </c>
+    </row>
+    <row r="493" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A493" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="B493" s="4">
+        <v>-11.985799999999999</v>
+      </c>
+      <c r="C493" s="4">
+        <v>32.903300000000002</v>
+      </c>
+      <c r="D493" s="4">
+        <v>397.05500000000001</v>
+      </c>
+      <c r="E493" s="4">
+        <v>-0.1552</v>
+      </c>
+      <c r="F493" s="4">
+        <v>0.98340000000000005</v>
+      </c>
+      <c r="G493" s="4">
+        <v>9.3700000000000006E-2</v>
+      </c>
+      <c r="H493" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I493" s="4">
+        <v>-2.7128999999999999</v>
+      </c>
+      <c r="J493" s="4">
+        <v>32.628100000000003</v>
+      </c>
+      <c r="K493" s="4">
+        <v>368.8535</v>
+      </c>
+      <c r="L493" s="4">
+        <v>1.6584000000000001</v>
+      </c>
+      <c r="M493" s="4">
+        <v>20.017499999999998</v>
+      </c>
+      <c r="N493" s="4">
+        <v>375.23169999999999</v>
+      </c>
+    </row>
+    <row r="494" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A494" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="B494" s="4">
+        <v>-11.985799999999999</v>
+      </c>
+      <c r="C494" s="4">
+        <v>32.903300000000002</v>
+      </c>
+      <c r="D494" s="4">
+        <v>397.05500000000001</v>
+      </c>
+      <c r="E494" s="4">
+        <v>-0.1552</v>
+      </c>
+      <c r="F494" s="4">
+        <v>0.98340000000000005</v>
+      </c>
+      <c r="G494" s="4">
+        <v>9.3700000000000006E-2</v>
+      </c>
+      <c r="H494" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I494" s="4">
+        <v>-11.4267</v>
+      </c>
+      <c r="J494" s="4">
+        <v>30.782399999999999</v>
+      </c>
+      <c r="K494" s="4">
+        <v>361.8655</v>
+      </c>
+      <c r="L494" s="4">
+        <v>-5.7477999999999998</v>
+      </c>
+      <c r="M494" s="4">
+        <v>52.383699999999997</v>
+      </c>
+      <c r="N494" s="4">
+        <v>398.33929999999998</v>
+      </c>
+    </row>
+    <row r="495" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A495" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="B495" s="4">
+        <v>-15.157</v>
+      </c>
+      <c r="C495" s="4">
+        <v>3.5619000000000001</v>
+      </c>
+      <c r="D495" s="4">
+        <v>572.53309999999999</v>
+      </c>
+      <c r="E495" s="4">
+        <v>-0.20380000000000001</v>
+      </c>
+      <c r="F495" s="4">
+        <v>-0.90069999999999995</v>
+      </c>
+      <c r="G495" s="4">
+        <v>0.38369999999999999</v>
+      </c>
+      <c r="H495" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I495" s="4">
+        <v>28.691600000000001</v>
+      </c>
+      <c r="J495" s="4">
+        <v>-35.002400000000002</v>
+      </c>
+      <c r="K495" s="4">
+        <v>568.50009999999997</v>
+      </c>
+      <c r="L495" s="4">
+        <v>-20.4496</v>
+      </c>
+      <c r="M495" s="4">
+        <v>-25.546399999999998</v>
+      </c>
+      <c r="N495" s="4">
+        <v>583.22320000000002</v>
+      </c>
+    </row>
+    <row r="496" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A496" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="B496" s="4">
+        <v>-15.157</v>
+      </c>
+      <c r="C496" s="4">
+        <v>3.5619000000000001</v>
+      </c>
+      <c r="D496" s="4">
+        <v>572.53309999999999</v>
+      </c>
+      <c r="E496" s="4">
+        <v>-0.20380000000000001</v>
+      </c>
+      <c r="F496" s="4">
+        <v>-0.90069999999999995</v>
+      </c>
+      <c r="G496" s="4">
+        <v>0.38369999999999999</v>
+      </c>
+      <c r="H496" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I496" s="4">
+        <v>-3.6842999999999999</v>
+      </c>
+      <c r="J496" s="4">
+        <v>-10.914300000000001</v>
+      </c>
+      <c r="K496" s="4">
+        <v>606.88800000000003</v>
+      </c>
+      <c r="L496" s="4">
+        <v>-38.945099999999996</v>
+      </c>
+      <c r="M496" s="4">
+        <v>-9.1234999999999999</v>
+      </c>
+      <c r="N496" s="4">
+        <v>610.73429999999996</v>
+      </c>
+    </row>
+    <row r="497" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A497" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="B497" s="4">
+        <v>-15.157</v>
+      </c>
+      <c r="C497" s="4">
+        <v>3.5619000000000001</v>
+      </c>
+      <c r="D497" s="4">
+        <v>572.53309999999999</v>
+      </c>
+      <c r="E497" s="4">
+        <v>-0.20380000000000001</v>
+      </c>
+      <c r="F497" s="4">
+        <v>-0.90069999999999995</v>
+      </c>
+      <c r="G497" s="4">
+        <v>0.38369999999999999</v>
+      </c>
+      <c r="H497" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I497" s="4">
+        <v>-32.942799999999998</v>
+      </c>
+      <c r="J497" s="4">
+        <v>-18.354299999999999</v>
+      </c>
+      <c r="K497" s="4">
+        <v>594.577</v>
+      </c>
+      <c r="L497" s="4">
+        <v>-46.310899999999997</v>
+      </c>
+      <c r="M497" s="4">
+        <v>-25.613900000000001</v>
+      </c>
+      <c r="N497" s="4">
+        <v>561.29200000000003</v>
+      </c>
+    </row>
+    <row r="498" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A498" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="B498" s="4">
+        <v>-15.157</v>
+      </c>
+      <c r="C498" s="4">
+        <v>3.5619000000000001</v>
+      </c>
+      <c r="D498" s="4">
+        <v>572.53309999999999</v>
+      </c>
+      <c r="E498" s="4">
+        <v>-0.20380000000000001</v>
+      </c>
+      <c r="F498" s="4">
+        <v>-0.90069999999999995</v>
+      </c>
+      <c r="G498" s="4">
+        <v>0.38369999999999999</v>
+      </c>
+      <c r="H498" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I498" s="4">
+        <v>32.584000000000003</v>
+      </c>
+      <c r="J498" s="4">
+        <v>-19.0932</v>
+      </c>
+      <c r="K498" s="4">
+        <v>597.52509999999995</v>
+      </c>
+      <c r="L498" s="4">
+        <v>35.414700000000003</v>
+      </c>
+      <c r="M498" s="4">
+        <v>24.853300000000001</v>
+      </c>
+      <c r="N498" s="4">
+        <v>556.19380000000001</v>
+      </c>
+    </row>
+    <row r="499" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A499" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="B499" s="4">
+        <v>-15.157</v>
+      </c>
+      <c r="C499" s="4">
+        <v>3.5619000000000001</v>
+      </c>
+      <c r="D499" s="4">
+        <v>572.53309999999999</v>
+      </c>
+      <c r="E499" s="4">
+        <v>-0.20380000000000001</v>
+      </c>
+      <c r="F499" s="4">
+        <v>-0.90069999999999995</v>
+      </c>
+      <c r="G499" s="4">
+        <v>0.38369999999999999</v>
+      </c>
+      <c r="H499" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I499" s="4">
+        <v>-3.7768000000000002</v>
+      </c>
+      <c r="J499" s="4">
+        <v>-41.714100000000002</v>
+      </c>
+      <c r="K499" s="4">
+        <v>556.19489999999996</v>
+      </c>
+      <c r="L499" s="4">
+        <v>3.6040000000000001</v>
+      </c>
+      <c r="M499" s="4">
+        <v>-9.9588999999999999</v>
+      </c>
+      <c r="N499" s="4">
+        <v>526.77760000000001</v>
+      </c>
+    </row>
+    <row r="500" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A500" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="B500" s="4">
+        <v>-15.157</v>
+      </c>
+      <c r="C500" s="4">
+        <v>3.5619000000000001</v>
+      </c>
+      <c r="D500" s="4">
+        <v>572.53309999999999</v>
+      </c>
+      <c r="E500" s="4">
+        <v>-0.20380000000000001</v>
+      </c>
+      <c r="F500" s="4">
+        <v>-0.90069999999999995</v>
+      </c>
+      <c r="G500" s="4">
+        <v>0.38369999999999999</v>
+      </c>
+      <c r="H500" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I500" s="4">
+        <v>36.404899999999998</v>
+      </c>
+      <c r="J500" s="4">
+        <v>-11.6593</v>
+      </c>
+      <c r="K500" s="4">
+        <v>613.79010000000005</v>
+      </c>
+      <c r="L500" s="4">
+        <v>38.1038</v>
+      </c>
+      <c r="M500" s="4">
+        <v>15.6417</v>
+      </c>
+      <c r="N500" s="4">
+        <v>608.14980000000003</v>
+      </c>
+    </row>
+    <row r="501" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A501" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="B501" s="4">
+        <v>-15.157</v>
+      </c>
+      <c r="C501" s="4">
+        <v>3.5619000000000001</v>
+      </c>
+      <c r="D501" s="4">
+        <v>572.53309999999999</v>
+      </c>
+      <c r="E501" s="4">
+        <v>-0.20380000000000001</v>
+      </c>
+      <c r="F501" s="4">
+        <v>-0.90069999999999995</v>
+      </c>
+      <c r="G501" s="4">
+        <v>0.38369999999999999</v>
+      </c>
+      <c r="H501" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I501" s="4">
+        <v>10.893700000000001</v>
+      </c>
+      <c r="J501" s="4">
+        <v>-0.42770000000000002</v>
+      </c>
+      <c r="K501" s="4">
+        <v>623.5394</v>
+      </c>
+      <c r="L501" s="4">
+        <v>7.6257999999999999</v>
+      </c>
+      <c r="M501" s="4">
+        <v>47.282800000000002</v>
+      </c>
+      <c r="N501" s="4">
+        <v>614.63909999999998</v>
+      </c>
+    </row>
+    <row r="502" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A502" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="B502" s="4">
+        <v>-15.157</v>
+      </c>
+      <c r="C502" s="4">
+        <v>3.5619000000000001</v>
+      </c>
+      <c r="D502" s="4">
+        <v>572.53309999999999</v>
+      </c>
+      <c r="E502" s="4">
+        <v>-0.20380000000000001</v>
+      </c>
+      <c r="F502" s="4">
+        <v>-0.90069999999999995</v>
+      </c>
+      <c r="G502" s="4">
+        <v>0.38369999999999999</v>
+      </c>
+      <c r="H502" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I502" s="4">
+        <v>10.893700000000001</v>
+      </c>
+      <c r="J502" s="4">
+        <v>-0.42770000000000002</v>
+      </c>
+      <c r="K502" s="4">
+        <v>623.5394</v>
+      </c>
+      <c r="L502" s="4">
+        <v>7.6257999999999999</v>
+      </c>
+      <c r="M502" s="4">
+        <v>47.282800000000002</v>
+      </c>
+      <c r="N502" s="4">
+        <v>614.63909999999998</v>
+      </c>
+    </row>
+    <row r="503" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A503" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="B503" s="4">
+        <v>-15.157</v>
+      </c>
+      <c r="C503" s="4">
+        <v>3.5619000000000001</v>
+      </c>
+      <c r="D503" s="4">
+        <v>572.53309999999999</v>
+      </c>
+      <c r="E503" s="4">
+        <v>-0.20380000000000001</v>
+      </c>
+      <c r="F503" s="4">
+        <v>-0.90069999999999995</v>
+      </c>
+      <c r="G503" s="4">
+        <v>0.38369999999999999</v>
+      </c>
+      <c r="H503" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I503" s="4">
+        <v>-38.216099999999997</v>
+      </c>
+      <c r="J503" s="4">
+        <v>-7.6468999999999996</v>
+      </c>
+      <c r="K503" s="4">
+        <v>611.48050000000001</v>
+      </c>
+      <c r="L503" s="4">
+        <v>-45.676400000000001</v>
+      </c>
+      <c r="M503" s="4">
+        <v>34.161700000000003</v>
+      </c>
+      <c r="N503" s="4">
+        <v>570.39170000000001</v>
+      </c>
+    </row>
+    <row r="504" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A504" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="B504" s="4">
+        <v>-15.157</v>
+      </c>
+      <c r="C504" s="4">
+        <v>3.5619000000000001</v>
+      </c>
+      <c r="D504" s="4">
+        <v>572.53309999999999</v>
+      </c>
+      <c r="E504" s="4">
+        <v>-0.20380000000000001</v>
+      </c>
+      <c r="F504" s="4">
+        <v>-0.90069999999999995</v>
+      </c>
+      <c r="G504" s="4">
+        <v>0.38369999999999999</v>
+      </c>
+      <c r="H504" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I504" s="4">
+        <v>-67.457099999999997</v>
+      </c>
+      <c r="J504" s="4">
+        <v>-5.1162000000000001</v>
+      </c>
+      <c r="K504" s="4">
+        <v>534.36090000000002</v>
+      </c>
+      <c r="L504" s="4">
+        <v>-32.940399999999997</v>
+      </c>
+      <c r="M504" s="4">
+        <v>33.776499999999999</v>
+      </c>
+      <c r="N504" s="4">
+        <v>532.80949999999996</v>
       </c>
     </row>
   </sheetData>
